--- a/Bases/Navegacao_Menu.xlsx
+++ b/Bases/Navegacao_Menu.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djdan\Documents\GitHub\Dash-Upmat\Bases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0190EFB3-D59E-42F9-A6B6-312F72243BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9DF9C49-BD03-4371-9A81-F8C18D46CF14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23880" yWindow="510" windowWidth="20730" windowHeight="11040" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
+    <workbookView xWindow="23880" yWindow="855" windowWidth="20640" windowHeight="11040" activeTab="1" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="Olitef" sheetId="2" r:id="rId1"/>
+    <sheet name="Kangaroo" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="32">
   <si>
     <t>Ordem</t>
   </si>
@@ -108,6 +109,30 @@
   </si>
   <si>
     <t>Listagem Prof x Estud</t>
+  </si>
+  <si>
+    <t>Respondentes</t>
+  </si>
+  <si>
+    <t>Inscrições 2026 - Part1</t>
+  </si>
+  <si>
+    <t>Inscrições 2026 - Part2</t>
+  </si>
+  <si>
+    <t>Busca Inscrições MKT 2026</t>
+  </si>
+  <si>
+    <t>Conversão 2026 - Part1</t>
+  </si>
+  <si>
+    <t>Conversão 2026 - Part2</t>
+  </si>
+  <si>
+    <t>Inscrições 2025</t>
+  </si>
+  <si>
+    <t>Busca Inscrições 2025</t>
   </si>
 </sst>
 </file>
@@ -497,7 +522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19030B0D-2A8E-4C3B-9DF6-B05FCD013344}">
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
@@ -828,10 +853,10 @@
         <v>9</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -839,40 +864,40 @@
         <v>9</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>6</v>
@@ -880,32 +905,32 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>5</v>
@@ -913,46 +938,46 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -960,10 +985,10 @@
         <v>14</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -971,7 +996,7 @@
         <v>14</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>6</v>
@@ -982,7 +1007,7 @@
         <v>15</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>19</v>
@@ -993,7 +1018,7 @@
         <v>15</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>4</v>
@@ -1004,7 +1029,7 @@
         <v>15</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>5</v>
@@ -1015,7 +1040,7 @@
         <v>15</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>6</v>
@@ -1026,10 +1051,10 @@
         <v>16</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -1037,10 +1062,10 @@
         <v>16</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1048,21 +1073,21 @@
         <v>16</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1070,10 +1095,10 @@
         <v>17</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1081,9 +1106,53 @@
         <v>17</v>
       </c>
       <c r="B53" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>17</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>18</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C55" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>18</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>18</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1094,4 +1163,447 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7F7F84F-51F4-4AA7-8488-D6CFB2C033F7}">
+  <dimension ref="A1:C39"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>4</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>4</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>4</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>5</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>5</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>5</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>6</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>6</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>6</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>7</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>7</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>7</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>8</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>8</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>8</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>9</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>9</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>10</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>10</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>10</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>11</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>11</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>11</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>12</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>12</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>12</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>13</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>13</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>13</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Bases/Navegacao_Menu.xlsx
+++ b/Bases/Navegacao_Menu.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djdan\Documents\GitHub\Dash-Upmat\Bases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9DF9C49-BD03-4371-9A81-F8C18D46CF14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B033D81F-E047-4BB0-9407-BAD3FB08F0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23880" yWindow="855" windowWidth="20640" windowHeight="11040" activeTab="1" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
   </bookViews>
   <sheets>
     <sheet name="Olitef" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="34">
   <si>
     <t>Ordem</t>
   </si>
@@ -120,19 +120,25 @@
     <t>Inscrições 2026 - Part2</t>
   </si>
   <si>
-    <t>Busca Inscrições MKT 2026</t>
-  </si>
-  <si>
-    <t>Conversão 2026 - Part1</t>
-  </si>
-  <si>
-    <t>Conversão 2026 - Part2</t>
-  </si>
-  <si>
     <t>Inscrições 2025</t>
   </si>
   <si>
-    <t>Busca Inscrições 2025</t>
+    <t>Censo - Part1</t>
+  </si>
+  <si>
+    <t>Censo - Part2</t>
+  </si>
+  <si>
+    <t>Listagem Inscrições 2026</t>
+  </si>
+  <si>
+    <t>Listagem Inscrições 2025</t>
+  </si>
+  <si>
+    <t>Meta 2026</t>
+  </si>
+  <si>
+    <t>Distribuição Plano</t>
   </si>
 </sst>
 </file>
@@ -522,7 +528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19030B0D-2A8E-4C3B-9DF6-B05FCD013344}">
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
@@ -658,7 +664,7 @@
         <v>8</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -669,18 +675,18 @@
         <v>8</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -691,7 +697,7 @@
         <v>9</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -702,7 +708,7 @@
         <v>9</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -713,18 +719,18 @@
         <v>9</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -735,7 +741,7 @@
         <v>10</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -746,7 +752,7 @@
         <v>10</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -757,18 +763,18 @@
         <v>10</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -779,7 +785,7 @@
         <v>11</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -790,7 +796,7 @@
         <v>11</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -801,18 +807,18 @@
         <v>11</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -823,7 +829,7 @@
         <v>20</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -834,7 +840,7 @@
         <v>20</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -845,18 +851,18 @@
         <v>20</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -867,7 +873,7 @@
         <v>24</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -878,7 +884,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -889,15 +895,15 @@
         <v>24</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>6</v>
@@ -911,18 +917,18 @@
         <v>17</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -933,18 +939,18 @@
         <v>16</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -955,18 +961,18 @@
         <v>21</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -977,18 +983,18 @@
         <v>18</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -999,18 +1005,18 @@
         <v>23</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -1021,7 +1027,7 @@
         <v>12</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -1032,7 +1038,7 @@
         <v>12</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -1043,18 +1049,18 @@
         <v>12</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -1065,7 +1071,7 @@
         <v>13</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1076,7 +1082,7 @@
         <v>13</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1087,18 +1093,18 @@
         <v>13</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1109,7 +1115,7 @@
         <v>14</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1120,18 +1126,18 @@
         <v>14</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1142,7 +1148,7 @@
         <v>15</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1153,6 +1159,17 @@
         <v>15</v>
       </c>
       <c r="C57" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>18</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1167,7 +1184,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7F7F84F-51F4-4AA7-8488-D6CFB2C033F7}">
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
@@ -1256,7 +1273,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>4</v>
@@ -1267,21 +1284,21 @@
         <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1289,10 +1306,10 @@
         <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1300,21 +1317,21 @@
         <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1322,10 +1339,10 @@
         <v>5</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -1333,18 +1350,18 @@
         <v>5</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>6</v>
@@ -1352,32 +1369,32 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>6</v>
@@ -1385,32 +1402,32 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>6</v>
@@ -1418,188 +1435,34 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <v>9</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
-        <v>9</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
-        <v>10</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
-        <v>10</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
-        <v>10</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
-        <v>11</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
-        <v>11</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
-        <v>11</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
-        <v>12</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
-        <v>12</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
-        <v>12</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
-        <v>13</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
-        <v>13</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
-        <v>13</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Bases/Navegacao_Menu.xlsx
+++ b/Bases/Navegacao_Menu.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djdan\Documents\GitHub\Dash-Upmat\Bases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B033D81F-E047-4BB0-9407-BAD3FB08F0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9006226C-A45E-40CF-828C-5BFFD9971FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
   </bookViews>
   <sheets>
     <sheet name="Olitef" sheetId="2" r:id="rId1"/>
     <sheet name="Kangaroo" sheetId="3" r:id="rId2"/>
+    <sheet name="Contatos Upmat" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="37">
   <si>
     <t>Ordem</t>
   </si>
@@ -139,6 +140,15 @@
   </si>
   <si>
     <t>Distribuição Plano</t>
+  </si>
+  <si>
+    <t>Migração Plano</t>
+  </si>
+  <si>
+    <t>Migração Experience</t>
+  </si>
+  <si>
+    <t>Contatos Upmat</t>
   </si>
 </sst>
 </file>
@@ -1184,7 +1194,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7F7F84F-51F4-4AA7-8488-D6CFB2C033F7}">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
@@ -1361,7 +1371,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>6</v>
@@ -1372,7 +1382,7 @@
         <v>7</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>6</v>
@@ -1383,7 +1393,7 @@
         <v>8</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>6</v>
@@ -1394,7 +1404,7 @@
         <v>9</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>6</v>
@@ -1405,7 +1415,7 @@
         <v>10</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>6</v>
@@ -1416,7 +1426,7 @@
         <v>11</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>6</v>
@@ -1427,7 +1437,7 @@
         <v>12</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>6</v>
@@ -1438,7 +1448,7 @@
         <v>13</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>6</v>
@@ -1449,7 +1459,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>6</v>
@@ -1457,12 +1467,77 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>16</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C26" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873DA74E-CB34-4CE6-BDAF-38AAD72725DF}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Bases/Navegacao_Menu.xlsx
+++ b/Bases/Navegacao_Menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djdan\Documents\GitHub\Dash-Upmat\Bases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9006226C-A45E-40CF-828C-5BFFD9971FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D759B9D-8B32-4447-9958-C7D2E1E9B110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="43">
   <si>
     <t>Ordem</t>
   </si>
@@ -124,31 +124,49 @@
     <t>Inscrições 2025</t>
   </si>
   <si>
-    <t>Censo - Part1</t>
-  </si>
-  <si>
-    <t>Censo - Part2</t>
-  </si>
-  <si>
-    <t>Listagem Inscrições 2026</t>
-  </si>
-  <si>
-    <t>Listagem Inscrições 2025</t>
-  </si>
-  <si>
-    <t>Meta 2026</t>
-  </si>
-  <si>
-    <t>Distribuição Plano</t>
-  </si>
-  <si>
-    <t>Migração Plano</t>
-  </si>
-  <si>
-    <t>Migração Experience</t>
-  </si>
-  <si>
     <t>Contatos Upmat</t>
+  </si>
+  <si>
+    <t>Respondentes 2026</t>
+  </si>
+  <si>
+    <t>Professores 2026</t>
+  </si>
+  <si>
+    <t>Estudantes 2026</t>
+  </si>
+  <si>
+    <t>Listagem de Escolas Censo</t>
+  </si>
+  <si>
+    <t>Potencial de Conversão Censo - Part2</t>
+  </si>
+  <si>
+    <t>Potencial de Conversão Censo - Part1</t>
+  </si>
+  <si>
+    <t>Potencial de Conversão Inscrições 2025 - Part2</t>
+  </si>
+  <si>
+    <t>Potencial de Conversão Inscrições 2025 - Part1</t>
+  </si>
+  <si>
+    <t>Listagem de Escolas Inscrições 2025 X 2026</t>
+  </si>
+  <si>
+    <t>Migração Experience 2025 x 2026</t>
+  </si>
+  <si>
+    <t>Migração de Plano 2025 x 2026</t>
+  </si>
+  <si>
+    <t>Distribuição por Plano 2026</t>
+  </si>
+  <si>
+    <t>Acompanhamento de Metas 2026</t>
+  </si>
+  <si>
+    <t>Listagem de Escolas Inscritas 2026</t>
   </si>
 </sst>
 </file>
@@ -1194,10 +1212,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7F7F84F-51F4-4AA7-8488-D6CFB2C033F7}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1283,7 +1301,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>4</v>
@@ -1294,7 +1312,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>6</v>
@@ -1302,13 +1320,13 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1316,10 +1334,10 @@
         <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -1327,21 +1345,21 @@
         <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1349,10 +1367,10 @@
         <v>5</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -1360,18 +1378,18 @@
         <v>5</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>6</v>
@@ -1379,10 +1397,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>6</v>
@@ -1390,10 +1408,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>6</v>
@@ -1401,10 +1419,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>6</v>
@@ -1412,10 +1430,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>6</v>
@@ -1423,10 +1441,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>6</v>
@@ -1434,10 +1452,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>6</v>
@@ -1445,10 +1463,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>6</v>
@@ -1456,10 +1474,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>6</v>
@@ -1467,10 +1485,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>6</v>
@@ -1478,12 +1496,34 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
+        <v>15</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
         <v>16</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="1" t="s">
+      <c r="B27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>17</v>
+      </c>
+      <c r="B28" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1513,7 +1553,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
@@ -1524,7 +1564,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -1535,7 +1575,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>6</v>

--- a/Bases/Navegacao_Menu.xlsx
+++ b/Bases/Navegacao_Menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djdan\Documents\GitHub\Dash-Upmat\Bases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D759B9D-8B32-4447-9958-C7D2E1E9B110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F48604D-70E4-490A-AE54-0DF5333F3566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="43">
   <si>
     <t>Ordem</t>
   </si>
@@ -1212,7 +1212,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7F7F84F-51F4-4AA7-8488-D6CFB2C033F7}">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.5703125" bestFit="1" customWidth="1"/>
@@ -1408,21 +1408,21 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>6</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>6</v>
@@ -1441,10 +1441,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>6</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>6</v>
@@ -1463,10 +1463,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>6</v>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>6</v>
@@ -1485,10 +1485,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>6</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>6</v>
@@ -1507,10 +1507,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>6</v>
@@ -1518,12 +1518,23 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
+        <v>16</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
         <v>17</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B29" t="s">
         <v>30</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C29" s="1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Bases/Navegacao_Menu.xlsx
+++ b/Bases/Navegacao_Menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djdan\Documents\GitHub\Dash-Upmat\Bases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F48604D-70E4-490A-AE54-0DF5333F3566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E796461A-2BF6-47DE-AC7F-0D2695825A9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="43">
   <si>
     <t>Ordem</t>
   </si>
@@ -1212,7 +1212,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7F7F84F-51F4-4AA7-8488-D6CFB2C033F7}">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.5703125" bestFit="1" customWidth="1"/>
@@ -1419,43 +1419,43 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>6</v>
@@ -1463,10 +1463,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>6</v>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>6</v>
@@ -1485,10 +1485,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>6</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>6</v>
@@ -1507,10 +1507,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>6</v>
@@ -1518,10 +1518,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>6</v>
@@ -1529,12 +1529,45 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
+        <v>14</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>15</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>16</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
         <v>17</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B32" t="s">
         <v>30</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C32" s="1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Bases/Navegacao_Menu.xlsx
+++ b/Bases/Navegacao_Menu.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djdan\Documents\GitHub\Dash-Upmat\Bases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E796461A-2BF6-47DE-AC7F-0D2695825A9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D076DE6-B4F6-4CCA-8193-FB1BB5C5D99B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="44">
   <si>
     <t>Ordem</t>
   </si>
@@ -151,9 +151,6 @@
     <t>Potencial de Conversão Inscrições 2025 - Part1</t>
   </si>
   <si>
-    <t>Listagem de Escolas Inscrições 2025 X 2026</t>
-  </si>
-  <si>
     <t>Migração Experience 2025 x 2026</t>
   </si>
   <si>
@@ -167,6 +164,12 @@
   </si>
   <si>
     <t>Listagem de Escolas Inscritas 2026</t>
+  </si>
+  <si>
+    <t>Listagem de Escolas Inscrições 2025</t>
+  </si>
+  <si>
+    <t>Seleção de Provas 2026</t>
   </si>
 </sst>
 </file>
@@ -1212,7 +1215,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7F7F84F-51F4-4AA7-8488-D6CFB2C033F7}">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.5703125" bestFit="1" customWidth="1"/>
@@ -1301,7 +1304,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>4</v>
@@ -1312,7 +1315,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>6</v>
@@ -1323,7 +1326,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>5</v>
@@ -1334,7 +1337,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>4</v>
@@ -1345,10 +1348,10 @@
         <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1356,10 +1359,10 @@
         <v>4</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1403,7 +1406,7 @@
         <v>39</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1425,7 +1428,7 @@
         <v>39</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -1436,7 +1439,7 @@
         <v>38</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -1447,7 +1450,7 @@
         <v>38</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -1458,7 +1461,7 @@
         <v>38</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -1466,29 +1469,29 @@
         <v>8</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>6</v>
@@ -1496,10 +1499,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>6</v>
@@ -1507,10 +1510,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>6</v>
@@ -1518,10 +1521,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>6</v>
@@ -1529,10 +1532,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>6</v>
@@ -1540,10 +1543,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>6</v>
@@ -1551,10 +1554,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>6</v>
@@ -1562,12 +1565,45 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
+        <v>15</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>16</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
         <v>17</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B34" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>18</v>
+      </c>
+      <c r="B35" t="s">
         <v>30</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C35" s="1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Bases/Navegacao_Menu.xlsx
+++ b/Bases/Navegacao_Menu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djdan\Documents\GitHub\Dash-Upmat\Bases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D076DE6-B4F6-4CCA-8193-FB1BB5C5D99B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29FD573D-2639-413A-B9F2-5A88A5F0FCEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="2" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
   </bookViews>
   <sheets>
     <sheet name="Olitef" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="46">
   <si>
     <t>Ordem</t>
   </si>
@@ -170,6 +170,12 @@
   </si>
   <si>
     <t>Seleção de Provas 2026</t>
+  </si>
+  <si>
+    <t>Engajamento de Estudantes - Simulado</t>
+  </si>
+  <si>
+    <t>Listagem Engajamento - Simulado</t>
   </si>
 </sst>
 </file>
@@ -1215,7 +1221,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7F7F84F-51F4-4AA7-8488-D6CFB2C033F7}">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.5703125" bestFit="1" customWidth="1"/>
@@ -1502,18 +1508,18 @@
         <v>9</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>6</v>
@@ -1521,21 +1527,21 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>6</v>
@@ -1543,10 +1549,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>6</v>
@@ -1554,10 +1560,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>6</v>
@@ -1565,10 +1571,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>6</v>
@@ -1576,10 +1582,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>6</v>
@@ -1587,10 +1593,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>6</v>
@@ -1598,12 +1604,56 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
+        <v>16</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>17</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
         <v>18</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B37" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>19</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>20</v>
+      </c>
+      <c r="B39" t="s">
         <v>30</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C39" s="1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Bases/Navegacao_Menu.xlsx
+++ b/Bases/Navegacao_Menu.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djdan\Documents\GitHub\Dash-Upmat\Bases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29FD573D-2639-413A-B9F2-5A88A5F0FCEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68DB45CC-83A2-415B-B91A-C4F557B06269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="2" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
   </bookViews>
   <sheets>
     <sheet name="Olitef" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="51">
   <si>
     <t>Ordem</t>
   </si>
@@ -176,6 +176,21 @@
   </si>
   <si>
     <t>Listagem Engajamento - Simulado</t>
+  </si>
+  <si>
+    <t>Engajamento de Estudantes - Prova</t>
+  </si>
+  <si>
+    <t>Listagem Engajamento - Prova</t>
+  </si>
+  <si>
+    <t>Comparativo de Inscrições 2025 x 2026</t>
+  </si>
+  <si>
+    <t>Comparativo de Experience 2025 x 2026</t>
+  </si>
+  <si>
+    <t>financeiro@upmat.com.br</t>
   </si>
 </sst>
 </file>
@@ -226,10 +241,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1221,7 +1237,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7F7F84F-51F4-4AA7-8488-D6CFB2C033F7}">
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.5703125" bestFit="1" customWidth="1"/>
@@ -1274,13 +1290,13 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1291,7 +1307,7 @@
         <v>26</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1302,29 +1318,29 @@
         <v>26</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>6</v>
+        <v>26</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1335,48 +1351,48 @@
         <v>41</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>4</v>
@@ -1384,65 +1400,65 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>4</v>
+        <v>43</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>6</v>
@@ -1450,21 +1466,21 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>5</v>
+        <v>40</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>4</v>
@@ -1472,10 +1488,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>5</v>
@@ -1483,54 +1499,54 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>6</v>
+        <v>39</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>4</v>
@@ -1538,43 +1554,43 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>6</v>
+        <v>38</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>6</v>
@@ -1582,43 +1598,43 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>6</v>
+        <v>37</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>6</v>
@@ -1626,21 +1642,21 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>6</v>
@@ -1648,12 +1664,210 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
+        <v>10</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>11</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>11</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>11</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>12</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>12</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>12</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>13</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>14</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>15</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>16</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>17</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>18</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>19</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
         <v>20</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B53" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>21</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>22</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>23</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>24</v>
+      </c>
+      <c r="B57" t="s">
         <v>30</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C57" s="1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Bases/Navegacao_Menu.xlsx
+++ b/Bases/Navegacao_Menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djdan\Documents\GitHub\Dash-Upmat\Bases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68DB45CC-83A2-415B-B91A-C4F557B06269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B66016E1-08B6-4CD7-BDCD-B3D7CD14CD38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="50">
   <si>
     <t>Ordem</t>
   </si>
@@ -119,9 +119,6 @@
   </si>
   <si>
     <t>Inscrições 2026 - Part2</t>
-  </si>
-  <si>
-    <t>Inscrições 2025</t>
   </si>
   <si>
     <t>Contatos Upmat</t>
@@ -241,11 +238,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1237,7 +1233,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7F7F84F-51F4-4AA7-8488-D6CFB2C033F7}">
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.5703125" bestFit="1" customWidth="1"/>
@@ -1295,8 +1291,8 @@
       <c r="B5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>50</v>
+      <c r="C5" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1339,8 +1335,8 @@
       <c r="B9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>50</v>
+      <c r="C9" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1348,7 +1344,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>4</v>
@@ -1359,7 +1355,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>6</v>
@@ -1370,7 +1366,7 @@
         <v>3</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>5</v>
@@ -1381,10 +1377,10 @@
         <v>3</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>50</v>
+        <v>40</v>
+      </c>
+      <c r="C13" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1392,7 +1388,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>4</v>
@@ -1403,7 +1399,7 @@
         <v>4</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>6</v>
@@ -1414,7 +1410,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>5</v>
@@ -1425,10 +1421,10 @@
         <v>4</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
+      </c>
+      <c r="C17" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1436,7 +1432,7 @@
         <v>5</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>4</v>
@@ -1447,7 +1443,7 @@
         <v>5</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>5</v>
@@ -1458,7 +1454,7 @@
         <v>5</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>6</v>
@@ -1469,10 +1465,10 @@
         <v>5</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>50</v>
+        <v>39</v>
+      </c>
+      <c r="C21" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -1480,7 +1476,7 @@
         <v>6</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>4</v>
@@ -1491,7 +1487,7 @@
         <v>6</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>5</v>
@@ -1502,7 +1498,7 @@
         <v>6</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>6</v>
@@ -1513,10 +1509,10 @@
         <v>6</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>50</v>
+        <v>38</v>
+      </c>
+      <c r="C25" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -1524,7 +1520,7 @@
         <v>7</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>6</v>
@@ -1535,7 +1531,7 @@
         <v>7</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>5</v>
@@ -1546,7 +1542,7 @@
         <v>7</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>4</v>
@@ -1557,10 +1553,10 @@
         <v>7</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>50</v>
+        <v>37</v>
+      </c>
+      <c r="C29" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1568,7 +1564,7 @@
         <v>8</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>5</v>
@@ -1579,7 +1575,7 @@
         <v>8</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>4</v>
@@ -1590,7 +1586,7 @@
         <v>8</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>6</v>
@@ -1601,10 +1597,10 @@
         <v>8</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>50</v>
+        <v>36</v>
+      </c>
+      <c r="C33" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1612,7 +1608,7 @@
         <v>9</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>5</v>
@@ -1623,7 +1619,7 @@
         <v>9</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>4</v>
@@ -1634,7 +1630,7 @@
         <v>9</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>6</v>
@@ -1645,7 +1641,7 @@
         <v>10</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>4</v>
@@ -1656,7 +1652,7 @@
         <v>10</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>6</v>
@@ -1667,7 +1663,7 @@
         <v>10</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>5</v>
@@ -1678,7 +1674,7 @@
         <v>11</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>4</v>
@@ -1689,7 +1685,7 @@
         <v>11</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>6</v>
@@ -1700,7 +1696,7 @@
         <v>11</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>5</v>
@@ -1711,7 +1707,7 @@
         <v>12</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>4</v>
@@ -1722,7 +1718,7 @@
         <v>12</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>6</v>
@@ -1733,7 +1729,7 @@
         <v>12</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>5</v>
@@ -1744,7 +1740,7 @@
         <v>13</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>6</v>
@@ -1755,7 +1751,7 @@
         <v>14</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>6</v>
@@ -1766,7 +1762,7 @@
         <v>15</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>6</v>
@@ -1774,21 +1770,21 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>6</v>
@@ -1796,21 +1792,21 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>6</v>
@@ -1818,21 +1814,21 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>6</v>
@@ -1840,21 +1836,21 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>6</v>
@@ -1862,12 +1858,111 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
+        <v>19</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>20</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>20</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>21</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>21</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>22</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>22</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>23</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
         <v>24</v>
       </c>
-      <c r="B57" t="s">
-        <v>30</v>
-      </c>
-      <c r="C57" s="1" t="s">
+      <c r="B65" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>25</v>
+      </c>
+      <c r="B66" t="s">
+        <v>29</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1897,7 +1992,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
@@ -1908,7 +2003,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -1919,7 +2014,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>6</v>

--- a/Bases/Navegacao_Menu.xlsx
+++ b/Bases/Navegacao_Menu.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djdan\Documents\GitHub\Dash-Upmat\Bases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B66016E1-08B6-4CD7-BDCD-B3D7CD14CD38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20777F3A-2EAA-4075-96DA-A0C41DFB369B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="3" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
   </bookViews>
   <sheets>
-    <sheet name="Olitef" sheetId="2" r:id="rId1"/>
-    <sheet name="Kangaroo" sheetId="3" r:id="rId2"/>
+    <sheet name="Olitef 2025" sheetId="2" r:id="rId1"/>
+    <sheet name="Kangaroo 2026" sheetId="3" r:id="rId2"/>
     <sheet name="Contatos Upmat" sheetId="4" r:id="rId3"/>
+    <sheet name="Olitef 2026" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="53">
   <si>
     <t>Ordem</t>
   </si>
@@ -188,6 +189,15 @@
   </si>
   <si>
     <t>financeiro@upmat.com.br</t>
+  </si>
+  <si>
+    <t>Inscrições 2025</t>
+  </si>
+  <si>
+    <t>Busca Inscrições 2025</t>
+  </si>
+  <si>
+    <t>Listagem de Escolas Inscritas 2026 (B3)</t>
   </si>
 </sst>
 </file>
@@ -238,10 +248,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1233,7 +1244,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7F7F84F-51F4-4AA7-8488-D6CFB2C033F7}">
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.5703125" bestFit="1" customWidth="1"/>
@@ -1748,54 +1759,54 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>5</v>
@@ -1803,10 +1814,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>6</v>
@@ -1814,10 +1825,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>5</v>
@@ -1825,54 +1836,54 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>6</v>
@@ -1880,10 +1891,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>5</v>
@@ -1891,54 +1902,54 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>6</v>
@@ -1946,24 +1957,189 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
+        <v>19</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>20</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>20</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>21</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>21</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>22</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>22</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>23</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>23</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>23</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>24</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>24</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>24</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
         <v>25</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B79" t="s">
         <v>29</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>6</v>
+      <c r="C79" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
+        <v>25</v>
+      </c>
+      <c r="B80" t="s">
+        <v>29</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>25</v>
+      </c>
+      <c r="B81" t="s">
+        <v>29</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2023,4 +2199,425 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F446C31-FA66-4630-B110-19ECB8E7DF76}">
+  <dimension ref="A1:C37"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="42.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>2</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>3</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>4</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>4</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>4</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>5</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>5</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>5</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>5</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>6</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>6</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>6</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>6</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>7</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>7</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>7</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>7</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>8</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>9</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>10</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>11</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>12</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>13</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>14</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>15</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>16</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>17</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>18</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Bases/Navegacao_Menu.xlsx
+++ b/Bases/Navegacao_Menu.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djdan\Documents\GitHub\Dash-Upmat\Bases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20777F3A-2EAA-4075-96DA-A0C41DFB369B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA80270D-1EA3-4985-B024-249E7D277F98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="3" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="54">
   <si>
     <t>Ordem</t>
   </si>
@@ -198,6 +198,9 @@
   </si>
   <si>
     <t>Listagem de Escolas Inscritas 2026 (B3)</t>
+  </si>
+  <si>
+    <t>Alcance nas Cidades</t>
   </si>
 </sst>
 </file>
@@ -248,11 +251,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2203,7 +2205,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F446C31-FA66-4630-B110-19ECB8E7DF76}">
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.5703125" bestFit="1" customWidth="1"/>
@@ -2228,7 +2230,7 @@
       <c r="B2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2272,7 +2274,7 @@
       <c r="B6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2501,40 +2503,40 @@
         <v>8</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>6</v>
@@ -2542,10 +2544,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>6</v>
@@ -2553,10 +2555,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>6</v>
@@ -2564,10 +2566,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>6</v>
@@ -2575,10 +2577,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>6</v>
@@ -2586,10 +2588,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>6</v>
@@ -2597,10 +2599,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>6</v>
@@ -2608,12 +2610,56 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
+        <v>15</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>16</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>17</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
         <v>18</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B40" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>19</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C41" s="1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Bases/Navegacao_Menu.xlsx
+++ b/Bases/Navegacao_Menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djdan\Documents\GitHub\Dash-Upmat\Bases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA80270D-1EA3-4985-B024-249E7D277F98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FAB5870-6691-4CD1-B747-E35CFFBDDEEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="3" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="61">
   <si>
     <t>Ordem</t>
   </si>
@@ -194,13 +194,34 @@
     <t>Inscrições 2025</t>
   </si>
   <si>
-    <t>Busca Inscrições 2025</t>
-  </si>
-  <si>
     <t>Listagem de Escolas Inscritas 2026 (B3)</t>
   </si>
   <si>
     <t>Alcance nas Cidades</t>
+  </si>
+  <si>
+    <t>Listagem de Escolas Inscritas 2025 x 2026</t>
+  </si>
+  <si>
+    <t>Potencial de Conversão 2025 - Part1</t>
+  </si>
+  <si>
+    <t>Potencial de Conversão 2025 - Part2</t>
+  </si>
+  <si>
+    <t>Professores 2026 (B3)</t>
+  </si>
+  <si>
+    <t>Engajamento Estudantes 2025</t>
+  </si>
+  <si>
+    <t>Listagem de Escolas Inscritas 2024</t>
+  </si>
+  <si>
+    <t>Potencial de Conversão 2024 - Part1</t>
+  </si>
+  <si>
+    <t>Potencial de Conversão 2024 - Part2</t>
   </si>
 </sst>
 </file>
@@ -2205,7 +2226,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F446C31-FA66-4630-B110-19ECB8E7DF76}">
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.5703125" bestFit="1" customWidth="1"/>
@@ -2316,7 +2337,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>19</v>
@@ -2327,7 +2348,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>6</v>
@@ -2371,7 +2392,7 @@
         <v>5</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>19</v>
@@ -2382,7 +2403,7 @@
         <v>5</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>4</v>
@@ -2393,7 +2414,7 @@
         <v>5</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>5</v>
@@ -2404,7 +2425,7 @@
         <v>5</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>6</v>
@@ -2415,7 +2436,7 @@
         <v>6</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>19</v>
@@ -2426,7 +2447,7 @@
         <v>6</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>4</v>
@@ -2437,7 +2458,7 @@
         <v>6</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>5</v>
@@ -2448,7 +2469,7 @@
         <v>6</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>6</v>
@@ -2459,7 +2480,7 @@
         <v>7</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>19</v>
@@ -2470,7 +2491,7 @@
         <v>7</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>4</v>
@@ -2481,7 +2502,7 @@
         <v>7</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>5</v>
@@ -2492,7 +2513,7 @@
         <v>7</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>6</v>
@@ -2503,7 +2524,7 @@
         <v>8</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>19</v>
@@ -2514,7 +2535,7 @@
         <v>8</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>4</v>
@@ -2525,7 +2546,7 @@
         <v>8</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>5</v>
@@ -2536,7 +2557,7 @@
         <v>8</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>6</v>
@@ -2569,7 +2590,7 @@
         <v>11</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>6</v>
@@ -2580,7 +2601,7 @@
         <v>12</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>6</v>
@@ -2602,40 +2623,40 @@
         <v>14</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>6</v>
@@ -2643,25 +2664,138 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
+        <v>15</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>15</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>15</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>16</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>17</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>18</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
         <v>19</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="B47" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>20</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>21</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>22</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="1"/>
+      <c r="C51" s="1"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Bases/Navegacao_Menu.xlsx
+++ b/Bases/Navegacao_Menu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djdan\Documents\GitHub\Dash-Upmat\Bases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FAB5870-6691-4CD1-B747-E35CFFBDDEEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A41AA8E-60E6-4809-A56D-F5361B30E5A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="3" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
   </bookViews>
   <sheets>
     <sheet name="Olitef 2025" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="62">
   <si>
     <t>Ordem</t>
   </si>
@@ -222,6 +222,9 @@
   </si>
   <si>
     <t>Potencial de Conversão 2024 - Part2</t>
+  </si>
+  <si>
+    <t>Experience 2026</t>
   </si>
 </sst>
 </file>
@@ -1267,7 +1270,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7F7F84F-51F4-4AA7-8488-D6CFB2C033F7}">
-  <dimension ref="A1:C81"/>
+  <dimension ref="A1:C82"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.5703125" bestFit="1" customWidth="1"/>
@@ -1774,32 +1777,32 @@
         <v>13</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -1807,32 +1810,32 @@
         <v>14</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1840,32 +1843,32 @@
         <v>15</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1873,32 +1876,32 @@
         <v>16</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -1906,32 +1909,32 @@
         <v>17</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -1939,32 +1942,32 @@
         <v>18</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -1972,32 +1975,32 @@
         <v>19</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>34</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>34</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -2005,21 +2008,21 @@
         <v>20</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -2027,21 +2030,21 @@
         <v>21</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -2049,21 +2052,21 @@
         <v>22</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -2071,15 +2074,15 @@
         <v>23</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>30</v>
@@ -2090,13 +2093,13 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -2104,64 +2107,75 @@
         <v>24</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>25</v>
       </c>
-      <c r="B79" t="s">
-        <v>29</v>
+      <c r="B79" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B80" t="s">
         <v>29</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B81" t="s">
         <v>29</v>
       </c>
       <c r="C81" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>26</v>
+      </c>
+      <c r="B82" t="s">
+        <v>29</v>
+      </c>
+      <c r="C82" s="1" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Bases/Navegacao_Menu.xlsx
+++ b/Bases/Navegacao_Menu.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djdan\Documents\GitHub\Dash-Upmat\Bases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A41AA8E-60E6-4809-A56D-F5361B30E5A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4816A14F-C5D6-46C5-9922-4A09F63E7DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="63">
   <si>
     <t>Ordem</t>
   </si>
@@ -225,6 +225,9 @@
   </si>
   <si>
     <t>Experience 2026</t>
+  </si>
+  <si>
+    <t>Engajamento Experience 2026</t>
   </si>
 </sst>
 </file>
@@ -1270,7 +1273,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7F7F84F-51F4-4AA7-8488-D6CFB2C033F7}">
-  <dimension ref="A1:C82"/>
+  <dimension ref="A1:C87"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.5703125" bestFit="1" customWidth="1"/>
@@ -1601,7 +1604,7 @@
         <v>8</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>5</v>
@@ -1612,7 +1615,7 @@
         <v>8</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>4</v>
@@ -1623,7 +1626,7 @@
         <v>8</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>6</v>
@@ -1631,13 +1634,13 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C33" t="s">
-        <v>49</v>
+        <v>28</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1645,10 +1648,10 @@
         <v>9</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -1656,21 +1659,21 @@
         <v>9</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -1678,7 +1681,7 @@
         <v>10</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>4</v>
@@ -1689,7 +1692,7 @@
         <v>10</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>6</v>
@@ -1697,13 +1700,13 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -1711,10 +1714,10 @@
         <v>11</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -1722,21 +1725,21 @@
         <v>11</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -1744,10 +1747,10 @@
         <v>12</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -1755,21 +1758,21 @@
         <v>12</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -1777,21 +1780,21 @@
         <v>13</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -1799,10 +1802,10 @@
         <v>14</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -1810,21 +1813,21 @@
         <v>14</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1832,10 +1835,10 @@
         <v>15</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1843,21 +1846,21 @@
         <v>15</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1865,10 +1868,10 @@
         <v>16</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1876,32 +1879,32 @@
         <v>16</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>5</v>
+        <v>36</v>
+      </c>
+      <c r="C57" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -1909,29 +1912,29 @@
         <v>17</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>5</v>
@@ -1942,29 +1945,29 @@
         <v>18</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>5</v>
@@ -1975,32 +1978,32 @@
         <v>19</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -2008,40 +2011,40 @@
         <v>20</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>6</v>
@@ -2049,10 +2052,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>5</v>
@@ -2060,65 +2063,65 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>5</v>
@@ -2126,32 +2129,32 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>26</v>
-      </c>
-      <c r="B80" t="s">
-        <v>29</v>
+        <v>24</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>5</v>
@@ -2159,10 +2162,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>26</v>
-      </c>
-      <c r="B81" t="s">
-        <v>29</v>
+        <v>25</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>6</v>
@@ -2170,12 +2173,67 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
+        <v>25</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
         <v>26</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B83" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>26</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>27</v>
+      </c>
+      <c r="B85" t="s">
         <v>29</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C85" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>27</v>
+      </c>
+      <c r="B86" t="s">
+        <v>29</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>27</v>
+      </c>
+      <c r="B87" t="s">
+        <v>29</v>
+      </c>
+      <c r="C87" s="1" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Bases/Navegacao_Menu.xlsx
+++ b/Bases/Navegacao_Menu.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djdan\Documents\GitHub\Dash-Upmat\Bases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4816A14F-C5D6-46C5-9922-4A09F63E7DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B22DB098-0FC1-4E50-85E9-26DF93EDBF9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="4" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
   </bookViews>
   <sheets>
     <sheet name="Olitef 2025" sheetId="2" r:id="rId1"/>
     <sheet name="Kangaroo 2026" sheetId="3" r:id="rId2"/>
     <sheet name="Contatos Upmat" sheetId="4" r:id="rId3"/>
     <sheet name="Olitef 2026" sheetId="5" r:id="rId4"/>
+    <sheet name="Experience" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="63">
   <si>
     <t>Ordem</t>
   </si>
@@ -2872,4 +2873,183 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FA0C564-8652-48EB-AFAF-28B449B9D62C}">
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="42.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>3</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>4</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>4</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>4</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>4</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Bases/Navegacao_Menu.xlsx
+++ b/Bases/Navegacao_Menu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djdan\Documents\GitHub\Dash-Upmat\Bases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B22DB098-0FC1-4E50-85E9-26DF93EDBF9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBF5222B-6A8E-4F94-9706-B1CA93BF3F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="4" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="3" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
   </bookViews>
   <sheets>
     <sheet name="Olitef 2025" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,11 @@
     <sheet name="Contatos Upmat" sheetId="4" r:id="rId3"/>
     <sheet name="Olitef 2026" sheetId="5" r:id="rId4"/>
     <sheet name="Experience" sheetId="6" r:id="rId5"/>
+    <sheet name="Bebras 2026" sheetId="8" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Olitef 2026'!$A$1:$C$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="75">
   <si>
     <t>Ordem</t>
   </si>
@@ -229,6 +233,42 @@
   </si>
   <si>
     <t>Engajamento Experience 2026</t>
+  </si>
+  <si>
+    <t>Pedido de Medalhas 2025</t>
+  </si>
+  <si>
+    <t>Respondentes 2025</t>
+  </si>
+  <si>
+    <t>Estudantes 2025</t>
+  </si>
+  <si>
+    <t>Inscrições 2024 - Part1</t>
+  </si>
+  <si>
+    <t>Inscrições 2024 - Part2</t>
+  </si>
+  <si>
+    <t>Listagem de Escolas Inscrições 2024</t>
+  </si>
+  <si>
+    <t>Estudantes 2024</t>
+  </si>
+  <si>
+    <t>Respondentes 2024</t>
+  </si>
+  <si>
+    <t>Pedido de Medalhas 2024</t>
+  </si>
+  <si>
+    <t>Potencial de Conversão Inscrições 2024 - Part1</t>
+  </si>
+  <si>
+    <t>Potencial de Conversão Inscrições 2024 - Part2</t>
+  </si>
+  <si>
+    <t>Inscrições 2026 - Part3</t>
   </si>
 </sst>
 </file>
@@ -2410,10 +2450,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -2421,7 +2461,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>6</v>
@@ -2429,448 +2469,468 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>4</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>4</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>5</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>4</v>
-      </c>
-      <c r="B13" s="1" t="s">
+      <c r="C15" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>5</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>4</v>
-      </c>
-      <c r="B14" s="1" t="s">
+      <c r="C16" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>5</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>5</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>5</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <v>5</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="C17" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>5</v>
+      <c r="A18">
+        <v>6</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+      <c r="A19">
         <v>6</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+      <c r="A20">
         <v>6</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
+      <c r="A21">
         <v>6</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>6</v>
+      <c r="A22">
+        <v>7</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
+      <c r="A23">
         <v>7</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
+      <c r="A24">
         <v>7</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
+      <c r="A25">
         <v>7</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <v>7</v>
+      <c r="A26">
+        <v>8</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
+      <c r="A27">
         <v>8</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
+      <c r="A28">
         <v>8</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
+      <c r="A29">
         <v>8</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
-        <v>8</v>
+      <c r="A30">
+        <v>9</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
+      <c r="A31">
         <v>9</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>9</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>9</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>10</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
-        <v>10</v>
-      </c>
-      <c r="B32" s="1" t="s">
+      <c r="C34" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>11</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
-        <v>11</v>
-      </c>
-      <c r="B33" s="1" t="s">
+      <c r="C35" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>12</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
-        <v>12</v>
-      </c>
-      <c r="B34" s="1" t="s">
+      <c r="C36" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>13</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
-        <v>13</v>
-      </c>
-      <c r="B35" s="1" t="s">
+      <c r="C37" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>14</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
-        <v>14</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
-        <v>14</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
-        <v>14</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="C38" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
-        <v>14</v>
+      <c r="A39">
+        <v>15</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
+      <c r="A40">
         <v>15</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="1">
+      <c r="A41">
         <v>15</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="1">
+      <c r="A42">
         <v>15</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="1">
-        <v>15</v>
+      <c r="A43">
+        <v>16</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="1">
+      <c r="A44">
         <v>16</v>
       </c>
       <c r="B44" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>16</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>16</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>17</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="1">
-        <v>17</v>
-      </c>
-      <c r="B45" s="1" t="s">
+      <c r="C47" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>18</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="1">
-        <v>18</v>
-      </c>
-      <c r="B46" s="1" t="s">
+      <c r="C48" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>19</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="1">
-        <v>19</v>
-      </c>
-      <c r="B47" s="1" t="s">
+      <c r="C49" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>20</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="1">
-        <v>20</v>
-      </c>
-      <c r="B48" s="1" t="s">
+      <c r="C50" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>21</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="1">
-        <v>21</v>
-      </c>
-      <c r="B49" s="1" t="s">
+      <c r="C51" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>22</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="1">
-        <v>22</v>
-      </c>
-      <c r="B50" s="1" t="s">
+      <c r="C52" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>23</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="1"/>
-      <c r="C51" s="1"/>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="1"/>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="1"/>
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
+      <c r="C53" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C1" xr:uid="{7F446C31-FA66-4630-B110-19ECB8E7DF76}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3052,4 +3112,819 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AD31D2E-82F9-4A53-8E31-D57E1126423D}">
+  <dimension ref="A1:C77"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="42.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>2</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>2</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>3</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>3</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>3</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>4</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>4</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>4</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>4</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>5</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>5</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>5</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>5</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>6</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>6</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>6</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>6</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>7</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>7</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>7</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>8</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>8</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>8</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>9</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C32" s="1"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>10</v>
+      </c>
+      <c r="B33" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" s="1"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>11</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>11</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>11</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>12</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>12</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>12</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>13</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>13</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>13</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>16</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>16</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>16</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>17</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>17</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>17</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>18</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>18</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>18</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>14</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>15</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>11</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>11</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>11</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>12</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>12</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>12</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>13</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>13</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>13</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>16</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>16</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>16</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>17</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>17</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>17</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>18</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>18</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>18</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>14</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C72" s="1"/>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>15</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C73" s="1"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C74" s="1"/>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C75" s="1"/>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C76" s="1"/>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C77" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Bases/Navegacao_Menu.xlsx
+++ b/Bases/Navegacao_Menu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djdan\Documents\GitHub\Dash-Upmat\Bases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBF5222B-6A8E-4F94-9706-B1CA93BF3F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E9933E-9F7D-4D71-8044-ECB802058851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="3" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="4" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
   </bookViews>
   <sheets>
     <sheet name="Olitef 2025" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="88">
   <si>
     <t>Ordem</t>
   </si>
@@ -269,13 +269,52 @@
   </si>
   <si>
     <t>Inscrições 2026 - Part3</t>
+  </si>
+  <si>
+    <t>Grupo</t>
+  </si>
+  <si>
+    <t>OrdemGrupo</t>
+  </si>
+  <si>
+    <t>Url</t>
+  </si>
+  <si>
+    <t>Inscrições</t>
+  </si>
+  <si>
+    <t>Cadastros</t>
+  </si>
+  <si>
+    <t>Medalhas</t>
+  </si>
+  <si>
+    <t>data:image/svg+xml;base64,PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0iVVRGLTgiPz4KPHN2ZyB4bWxucz0iaHR0cDovL3d3dy53My5vcmcvMjAwMC9zdmciIHdpZHRoPSIyNCIgaGVpZ2h0PSIyNCIgdmlld0JveD0iMCAwIDI0IDI0IiBmaWxsPSJub25lIj4KICA8cGF0aCBkPSJNMTQuODc1IDE1LjEyNUMxNC4yOTE3IDE0LjU0MTcgMTQgMTMuODMzMyAxNCAxM0MxNCAxMi4xNjY3IDE0LjI5MTcgMTEuNDU4MyAxNC44NzUgMTAuODc1QzE1LjQ1ODMgMTAuMjkxNyAxNi4xNjY3IDEwIDE3IDEwQzE3LjgzMzMgMTAgMTguNTQxNyAxMC4yOTE3IDE5LjEyNSAxMC44NzVDMTkuNzA4MyAxMS40NTgzIDIwIDEyLjE2NjcgMjAgMTNDMjAgMTMuODMzMyAxOS43MDgzIDE0LjU0MTcgMTkuMTI1IDE1LjEyNUMxOC41NDE3IDE1LjcwODMgMTcuODMzMyAxNiAxNyAxNkMxNi4xNjY3IDE2IDE1LjQ1ODMgMTUuNzA4MyAxNC44NzUgMTUuMTI1Wk0xNy43MTMgMTMuNzEzQzE3LjkwNDMgMTMuNTIxIDE4IDEzLjI4MzMgMTggMTNDMTggMTIuNzE2NyAxNy45MDQgMTIuNDc5MyAxNy43MTIgMTIuMjg4QzE3LjUyIDEyLjA5NjcgMTcuMjgyNyAxMi4wMDA3IDE3IDEyQzE2LjcxNzMgMTEuOTk5MyAxNi40OCAxMi4wOTUzIDE2LjI4OCAxMi4yODhDMTYuMDk2IDEyLjQ4MDcgMTYgMTIuNzE4IDE2IDEzQzE2IDEzLjI4MiAxNi4wOTYgMTMuNTE5NyAxNi4yODggMTMuNzEzQzE2LjQ4IDEzLjkwNjMgMTYuNzE3MyAxNC4wMDIgMTcgMTRDMTcuMjgyNyAxMy45OTggMTcuNTIwMyAxMy45MDIgMTcuNzEzIDEzLjcxMk0xMiAyM0MxMS43MTY3IDIzIDExLjQ3OTMgMjIuOTA0IDExLjI4OCAyMi43MTJDMTEuMDk2NyAyMi41MiAxMS4wMDA3IDIyLjI4MjcgMTEgMjJWMjAuMUMxMSAxOS43NSAxMS4wODMzIDE5LjQyMSAxMS4yNSAxOS4xMTNDMTEuNDE2NyAxOC44MDUgMTEuNjUgMTguNTU5IDExLjk1IDE4LjM3NUMxMi40ODMzIDE4LjA1ODMgMTIuOTMzMyAxNy44MzczIDEzLjMgMTcuNzEyQzEzLjY2NjcgMTcuNTg2NyAxNC4xNTgzIDE3LjQ3NDMgMTQuNzc1IDE3LjM3NUMxNC45NzUgMTcuMzQxNyAxNS4xNzUgMTcuMzQ2IDE1LjM3NSAxNy4zODhDMTUuNTc1IDE3LjQzIDE1Ljc0MTcgMTcuNTI1NyAxNS44NzUgMTcuNjc1TDE3IDE5TDE4LjEgMTcuNjc1QzE4LjIzMzMgMTcuNTA4MyAxOC40IDE3LjQwODMgMTguNiAxNy4zNzVDMTguOCAxNy4zNDE3IDE5IDE3LjM0MTcgMTkuMiAxNy4zNzVDMTkuODE2NyAxNy40NzUgMjAuMzA4MyAxNy41ODc3IDIwLjY3NSAxNy43MTNDMjEuMDQxNyAxNy44MzgzIDIxLjQ5MTcgMTguMDU5IDIyLjAyNSAxOC4zNzVDMjIuMzI1IDE4LjU1ODMgMjIuNTYyNyAxOC44MDQzIDIyLjczOCAxOS4xMTNDMjIuOTEzMyAxOS40MjE3IDIzLjAwMDcgMTkuNzUwNyAyMyAyMC4xVjIyQzIzIDIyLjI4MzMgMjIuOTA0IDIyLjUyMSAyMi43MTIgMjIuNzEzQzIyLjUyIDIyLjkwNSAyMi4yODI3IDIzLjAwMDcgMjIgMjNIMTJaTTEyLjk3NSAyMUgxNi4wNUwxNC43IDE5LjM1QzE0LjQgMTkuNDMzMyAxNC4xMDgzIDE5LjU0MTcgMTMuODI1IDE5LjY3NUMxMy41NDE3IDE5LjgwODMgMTMuMjU4MyAxOS45NSAxMi45NzUgMjAuMVYyMVpNMTcuOTUgMjFIMjFWMjAuMUMyMC43MzMzIDE5LjkzMzMgMjAuNDU4MyAxOS43ODc3IDIwLjE3NSAxOS42NjNDMTkuODkxNyAxOS41MzgzIDE5LjYgMTkuNDM0IDE5LjMgMTkuMzVMMTcuOTUgMjFaTTUgMTlWNVY4LjQyNVY4VjE5Wk01IDIxQzQuNDUgMjEgMy45NzkgMjAuODA0MyAzLjU4NyAyMC40MTNDMy4xOTUgMjAuMDIxNyAyLjk5OTM0IDE5LjU1MDcgMyAxOVY1QzMgNC40NSAzLjE5NiAzLjk3OTMzIDMuNTg4IDMuNTg4QzMuOTggMy4xOTY2NyA0LjQ1MDY3IDMuMDAwNjcgNSAzSDE5QzE5LjU1IDMgMjAuMDIxIDMuMTk2IDIwLjQxMyAzLjU4OEMyMC44MDUgMy45OCAyMS4wMDA3IDQuNDUwNjcgMjEgNVYxMEMyMC43MzMzIDkuNjY2NjcgMjAuNDQxNyA5LjM1IDIwLjEyNSA5LjA1QzE5LjgwODMgOC43NSAxOS40MzMzIDguNTUgMTkgOC40NVY1SDVWMTlIOS4xNUM5LjEgMTkuMTgzMyA5LjA2MjY3IDE5LjM2NjcgOS4wMzggMTkuNTVDOS4wMTMzNCAxOS43MzMzIDkuMDAwNjcgMTkuOTE2NyA5IDIwLjFWMjFINVpNOCA5SDE0QzE0LjQzMzMgOC42NjY2NyAxNC45MDgzIDguNDE2NjcgMTUuNDI1IDguMjVDMTUuOTQxNyA4LjA4MzMzIDE2LjQ2NjcgOCAxNyA4QzE3IDcuNzE2NjcgMTYuOTA0IDcuNDc5MzMgMTYuNzEyIDcuMjg4QzE2LjUyIDcuMDk2NjcgMTYuMjgyNyA3LjAwMDY3IDE2IDdIOEM3LjcxNjY3IDcgNy40NzkzNCA3LjA5NiA3LjI4OCA3LjI4OEM3LjA5NjY3IDcuNDggNy4wMDA2NyA3LjcxNzMzIDcgOEM2Ljk5OTM0IDguMjgyNjcgNy4wOTUzNCA4LjUyMDMzIDcuMjg4IDguNzEzQzcuNDgwNjcgOC45MDU2NyA3LjcxOCA5LjAwMTMzIDggOVpNOCAxM0gxMkMxMiAxMi42NSAxMi4wMzc3IDEyLjMwODMgMTIuMTEzIDExLjk3NUMxMi4xODgzIDExLjY0MTcgMTIuMjkyMyAxMS4zMTY3IDEyLjQyNSAxMUg4QzcuNzE2NjcgMTEgNy40NzkzNCAxMS4wOTYgNy4yODggMTEuMjg4QzcuMDk2NjcgMTEuNDggNy4wMDA2NyAxMS43MTczIDcgMTJDNi45OTkzNCAxMi4yODI3IDcuMDk1MzQgMTIuNTIwMyA3LjI4OCAxMi43MTNDNy40ODA2NyAxMi45MDU3IDcuNzE4IDEzLjAwMTMgOCAxM1pNOCAxN0gxMC40NUMxMC42MzMzIDE2Ljg1IDEwLjgyOTMgMTYuNzE2NyAxMS4wMzggMTYuNkMxMS4yNDY3IDE2LjQ4MzMgMTEuNDU5IDE2LjM3NSAxMS42NzUgMTYuMjc1VjE2QzExLjY3NSAxNS43MzMzIDExLjYwNCAxNS41IDExLjQ2MiAxNS4zQzExLjMyIDE1LjEgMTEuMDU3NyAxNSAxMC42NzUgMTVIOEM3LjcxNjY3IDE1IDcuNDc5MzQgMTUuMDk2IDcuMjg4IDE1LjI4OEM3LjA5NjY3IDE1LjQ4IDcuMDAwNjcgMTUuNzE3MyA3IDE2QzYuOTk5MzQgMTYuMjgyNyA3LjA5NTM0IDE2LjUyMDMgNy4yODggMTYuNzEzQzcuNDgwNjcgMTYuOTA1NyA3LjcxOCAxNy4wMDEzIDggMTdaIiBmaWxsPSIjRkZENTRGIj48L3BhdGg+Cjwvc3ZnPgo=</t>
+  </si>
+  <si>
+    <t>data:image/svg+xml;base64,PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0iVVRGLTgiPz4KPHN2ZyB4bWxucz0iaHR0cDovL3d3dy53My5vcmcvMjAwMC9zdmciIHdpZHRoPSIyNCIgaGVpZ2h0PSIyNCIgdmlld0JveD0iMCAwIDI0IDI0IiBmaWxsPSJub25lIj4KICA8cGF0aCBkPSJNMTUgMTRDMTIuMzMgMTQgNyAxNS4zMyA3IDE4VjIwSDIzVjE4QzIzIDE1LjMzIDE3LjY3IDE0IDE1IDE0Wk02IDEwVjdINFYxMEgxVjEySDRWMTVINlYxMkg5VjEwTTE1IDEyQzE2LjA2MDkgMTIgMTcuMDc4MyAxMS41Nzg2IDE3LjgyODQgMTAuODI4NEMxOC41Nzg2IDEwLjA3ODMgMTkgOS4wNjA4NyAxOSA4QzE5IDYuOTM5MTMgMTguNTc4NiA1LjkyMTcyIDE3LjgyODQgNS4xNzE1N0MxNy4wNzgzIDQuNDIxNDMgMTYuMDYwOSA0IDE1IDRDMTMuOTM5MSA0IDEyLjkyMTcgNC40MjE0MyAxMi4xNzE2IDUuMTcxNTdDMTEuNDIxNCA1LjkyMTcyIDExIDYuOTM5MTMgMTEgOEMxMSA5LjA2MDg3IDExLjQyMTQgMTAuMDc4MyAxMi4xNzE2IDEwLjgyODRDMTIuOTIxNyAxMS41Nzg2IDEzLjkzOTEgMTIgMTUgMTJaIiBmaWxsPSIjRkZENTRGIj48L3BhdGg+Cjwvc3ZnPgo=</t>
+  </si>
+  <si>
+    <t>data:image/svg+xml;base64,PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0iVVRGLTgiPz4KPHN2ZyB4bWxucz0iaHR0cDovL3d3dy53My5vcmcvMjAwMC9zdmciIHdpZHRoPSIyNCIgaGVpZ2h0PSIyNCIgdmlld0JveD0iMCAwIDI0IDI0IiBmaWxsPSJub25lIj4KICA8cGF0aCBkPSJNNy4yMDk5NiAxNUwyLjY1OTk2IDcuMTRDMi40NjM3NiA2LjgwMDg3IDIuMzcxNDkgNi40MTE1OSAyLjM5NDYgNi4wMjA0OEMyLjQxNzcxIDUuNjI5MzcgMi41NTUxOCA1LjI1MzY2IDIuNzg5OTYgNC45NEw0LjM5OTk2IDIuOEM0LjU4NjI1IDIuNTUxNjEgNC44Mjc4MiAyLjM1IDUuMTA1NTMgMi4yMTExNUM1LjM4MzI0IDIuMDcyMjkgNS42ODk0NyAyIDUuOTk5OTYgMkgxOEMxOC4zMTA0IDIgMTguNjE2NyAyLjA3MjI5IDE4Ljg5NDQgMi4yMTExNUMxOS4xNzIxIDIuMzUgMTkuNDEzNyAyLjU1MTYxIDE5LjYgMi44TDIxLjIgNC45NEMyMS40MzYzIDUuMjUyNjUgMjEuNTc1NSA1LjYyNzg0IDIxLjYwMDQgNi4wMTg5N0MyMS42MjUzIDYuNDEwMSAyMS41MzQ3IDYuNzk5OTIgMjEuMzQgNy4xNEwxNi43OSAxNU0xMSAxMkw1LjExOTk2IDIuMk0xMyAxMkwxOC44OCAyLjJNNy45OTk5NiA3SDE2IiBzdHJva2U9IiNGRkQ1NEYiIHN0cm9rZS13aWR0aD0iMiIgc3Ryb2tlLWxpbmVjYXA9InJvdW5kIiBzdHJva2UtbGluZWpvaW49InJvdW5kIj48L3BhdGg+CiAgPHBhdGggZD0iTTEyIDIyQzE0Ljc2MTQgMjIgMTcgMTkuNzYxNCAxNyAxN0MxNyAxNC4yMzg2IDE0Ljc2MTQgMTIgMTIgMTJDOS4yMzg1OCAxMiA3IDE0LjIzODYgNyAxN0M3IDE5Ljc2MTQgOS4yMzg1OCAyMiAxMiAyMloiIHN0cm9rZT0iI0ZGRDU0RiIgc3Ryb2tlLXdpZHRoPSIyIiBzdHJva2UtbGluZWNhcD0icm91bmQiIHN0cm9rZS1saW5lam9pbj0icm91bmQiPjwvcGF0aD4KICA8cGF0aCBkPSJNMTIgMThWMTZIMTEuNSIgc3Ryb2tlPSIjRkZENTRGIiBzdHJva2Utd2lkdGg9IjIiIHN0cm9rZS1saW5lY2FwPSJyb3VuZCIgc3Ryb2tlLWxpbmVqb2luPSJyb3VuZCI+PC9wYXRoPgo8L3N2Zz4K</t>
+  </si>
+  <si>
+    <t>Canguru Experience 2026</t>
+  </si>
+  <si>
+    <t>Engajamento Canguru Experience 2026</t>
+  </si>
+  <si>
+    <t>Listagem Professores Canguru Experience 2026</t>
+  </si>
+  <si>
+    <t>Migração Canguru Experience 2025 x 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -293,6 +332,13 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -319,10 +365,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2937,7 +2984,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FA0C564-8652-48EB-AFAF-28B449B9D62C}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.5703125" bestFit="1" customWidth="1"/>
@@ -2960,7 +3007,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
@@ -2971,7 +3018,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>6</v>
@@ -2982,7 +3029,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -2990,13 +3037,13 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>5</v>
+        <v>84</v>
+      </c>
+      <c r="C5" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -3004,10 +3051,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -3015,32 +3062,32 @@
         <v>2</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>5</v>
+        <v>85</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -3048,10 +3095,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -3059,32 +3106,32 @@
         <v>3</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" t="s">
-        <v>49</v>
+        <v>86</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>4</v>
+        <v>86</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -3092,10 +3139,10 @@
         <v>4</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -3103,9 +3150,75 @@
         <v>4</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>4</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>4</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>5</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C18" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>5</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>5</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>5</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" t="s">
         <v>49</v>
       </c>
     </row>
@@ -3116,14 +3229,16 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AD31D2E-82F9-4A53-8E31-D57E1126423D}">
-  <dimension ref="A1:C77"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3133,8 +3248,17 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -3144,8 +3268,17 @@
       <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -3155,8 +3288,17 @@
       <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -3166,8 +3308,17 @@
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -3177,8 +3328,17 @@
       <c r="C5" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -3188,8 +3348,17 @@
       <c r="C6" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2</v>
       </c>
@@ -3199,8 +3368,17 @@
       <c r="C7" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2</v>
       </c>
@@ -3210,8 +3388,17 @@
       <c r="C8" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2</v>
       </c>
@@ -3221,8 +3408,17 @@
       <c r="C9" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>3</v>
       </c>
@@ -3232,8 +3428,17 @@
       <c r="C10" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>3</v>
       </c>
@@ -3243,8 +3448,17 @@
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>3</v>
       </c>
@@ -3254,8 +3468,17 @@
       <c r="C12" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>3</v>
       </c>
@@ -3265,8 +3488,17 @@
       <c r="C13" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>4</v>
       </c>
@@ -3276,8 +3508,17 @@
       <c r="C14" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
+        <v>78</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>4</v>
       </c>
@@ -3287,8 +3528,17 @@
       <c r="C15" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D15" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>4</v>
       </c>
@@ -3298,8 +3548,17 @@
       <c r="C16" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>78</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>4</v>
       </c>
@@ -3309,8 +3568,17 @@
       <c r="C17" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>5</v>
       </c>
@@ -3320,8 +3588,17 @@
       <c r="C18" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>5</v>
       </c>
@@ -3331,8 +3608,17 @@
       <c r="C19" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>5</v>
       </c>
@@ -3342,8 +3628,17 @@
       <c r="C20" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>5</v>
       </c>
@@ -3353,8 +3648,17 @@
       <c r="C21" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>6</v>
       </c>
@@ -3364,8 +3668,17 @@
       <c r="C22" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>6</v>
       </c>
@@ -3375,8 +3688,17 @@
       <c r="C23" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23" t="s">
+        <v>78</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>6</v>
       </c>
@@ -3386,8 +3708,17 @@
       <c r="C24" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24" t="s">
+        <v>78</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>6</v>
       </c>
@@ -3397,8 +3728,17 @@
       <c r="C25" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25" t="s">
+        <v>78</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+      <c r="F25" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>7</v>
       </c>
@@ -3408,8 +3748,17 @@
       <c r="C26" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D26" t="s">
+        <v>79</v>
+      </c>
+      <c r="E26">
+        <v>2</v>
+      </c>
+      <c r="F26" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>7</v>
       </c>
@@ -3419,8 +3768,17 @@
       <c r="C27" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
+        <v>79</v>
+      </c>
+      <c r="E27">
+        <v>2</v>
+      </c>
+      <c r="F27" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>7</v>
       </c>
@@ -3430,8 +3788,17 @@
       <c r="C28" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
+        <v>79</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+      <c r="F28" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>8</v>
       </c>
@@ -3441,8 +3808,17 @@
       <c r="C29" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E29">
+        <v>2</v>
+      </c>
+      <c r="F29" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>8</v>
       </c>
@@ -3452,8 +3828,17 @@
       <c r="C30" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D30" t="s">
+        <v>79</v>
+      </c>
+      <c r="E30">
+        <v>2</v>
+      </c>
+      <c r="F30" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>8</v>
       </c>
@@ -3463,8 +3848,17 @@
       <c r="C31" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D31" t="s">
+        <v>79</v>
+      </c>
+      <c r="E31">
+        <v>2</v>
+      </c>
+      <c r="F31" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>9</v>
       </c>
@@ -3472,8 +3866,17 @@
         <v>47</v>
       </c>
       <c r="C32" s="1"/>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D32" t="s">
+        <v>78</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>10</v>
       </c>
@@ -3481,8 +3884,17 @@
         <v>29</v>
       </c>
       <c r="C33" s="1"/>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D33" t="s">
+        <v>79</v>
+      </c>
+      <c r="E33">
+        <v>2</v>
+      </c>
+      <c r="F33" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>11</v>
       </c>
@@ -3492,8 +3904,17 @@
       <c r="C34" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D34" t="s">
+        <v>78</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>11</v>
       </c>
@@ -3503,8 +3924,17 @@
       <c r="C35" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D35" t="s">
+        <v>78</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="F35" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>11</v>
       </c>
@@ -3514,8 +3944,17 @@
       <c r="C36" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D36" t="s">
+        <v>78</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+      <c r="F36" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>12</v>
       </c>
@@ -3525,8 +3964,17 @@
       <c r="C37" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
+        <v>78</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+      <c r="F37" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>12</v>
       </c>
@@ -3536,8 +3984,17 @@
       <c r="C38" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D38" t="s">
+        <v>78</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>12</v>
       </c>
@@ -3547,8 +4004,17 @@
       <c r="C39" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D39" t="s">
+        <v>78</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+      <c r="F39" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>13</v>
       </c>
@@ -3558,8 +4024,17 @@
       <c r="C40" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D40" t="s">
+        <v>78</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+      <c r="F40" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>13</v>
       </c>
@@ -3569,8 +4044,17 @@
       <c r="C41" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D41" t="s">
+        <v>78</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+      <c r="F41" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>13</v>
       </c>
@@ -3580,10 +4064,19 @@
       <c r="C42" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D42" t="s">
+        <v>78</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+      <c r="F42" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>65</v>
@@ -3591,10 +4084,19 @@
       <c r="C43" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D43" t="s">
+        <v>79</v>
+      </c>
+      <c r="E43">
+        <v>2</v>
+      </c>
+      <c r="F43" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>65</v>
@@ -3602,10 +4104,19 @@
       <c r="C44" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D44" t="s">
+        <v>79</v>
+      </c>
+      <c r="E44">
+        <v>2</v>
+      </c>
+      <c r="F44" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>65</v>
@@ -3613,10 +4124,19 @@
       <c r="C45" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D45" t="s">
+        <v>79</v>
+      </c>
+      <c r="E45">
+        <v>2</v>
+      </c>
+      <c r="F45" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>64</v>
@@ -3624,10 +4144,19 @@
       <c r="C46" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D46" t="s">
+        <v>79</v>
+      </c>
+      <c r="E46">
+        <v>2</v>
+      </c>
+      <c r="F46" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>64</v>
@@ -3635,10 +4164,19 @@
       <c r="C47" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D47" t="s">
+        <v>79</v>
+      </c>
+      <c r="E47">
+        <v>2</v>
+      </c>
+      <c r="F47" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>64</v>
@@ -3646,10 +4184,19 @@
       <c r="C48" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D48" t="s">
+        <v>79</v>
+      </c>
+      <c r="E48">
+        <v>2</v>
+      </c>
+      <c r="F48" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>63</v>
@@ -3657,10 +4204,19 @@
       <c r="C49" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D49" t="s">
+        <v>80</v>
+      </c>
+      <c r="E49">
+        <v>3</v>
+      </c>
+      <c r="F49" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>63</v>
@@ -3668,10 +4224,19 @@
       <c r="C50" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D50" t="s">
+        <v>80</v>
+      </c>
+      <c r="E50">
+        <v>3</v>
+      </c>
+      <c r="F50" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>63</v>
@@ -3679,26 +4244,53 @@
       <c r="C51" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D51" t="s">
+        <v>80</v>
+      </c>
+      <c r="E51">
+        <v>3</v>
+      </c>
+      <c r="F51" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D52" t="s">
+        <v>78</v>
+      </c>
+      <c r="E52">
+        <v>1</v>
+      </c>
+      <c r="F52" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D53" t="s">
+        <v>78</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
+      <c r="F53" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>66</v>
@@ -3706,10 +4298,19 @@
       <c r="C54" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D54" t="s">
+        <v>78</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+      <c r="F54" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>66</v>
@@ -3717,10 +4318,19 @@
       <c r="C55" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D55" t="s">
+        <v>78</v>
+      </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
+      <c r="F55" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>66</v>
@@ -3728,10 +4338,19 @@
       <c r="C56" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D56" t="s">
+        <v>78</v>
+      </c>
+      <c r="E56">
+        <v>1</v>
+      </c>
+      <c r="F56" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>67</v>
@@ -3739,10 +4358,19 @@
       <c r="C57" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D57" t="s">
+        <v>78</v>
+      </c>
+      <c r="E57">
+        <v>1</v>
+      </c>
+      <c r="F57" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>67</v>
@@ -3750,10 +4378,19 @@
       <c r="C58" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D58" t="s">
+        <v>78</v>
+      </c>
+      <c r="E58">
+        <v>1</v>
+      </c>
+      <c r="F58" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>67</v>
@@ -3761,10 +4398,19 @@
       <c r="C59" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D59" t="s">
+        <v>78</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+      <c r="F59" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>68</v>
@@ -3772,10 +4418,19 @@
       <c r="C60" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D60" t="s">
+        <v>78</v>
+      </c>
+      <c r="E60">
+        <v>1</v>
+      </c>
+      <c r="F60" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>68</v>
@@ -3783,10 +4438,19 @@
       <c r="C61" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D61" t="s">
+        <v>78</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
+      <c r="F61" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>68</v>
@@ -3794,10 +4458,19 @@
       <c r="C62" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D62" t="s">
+        <v>78</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+      <c r="F62" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>69</v>
@@ -3805,10 +4478,19 @@
       <c r="C63" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D63" t="s">
+        <v>79</v>
+      </c>
+      <c r="E63">
+        <v>2</v>
+      </c>
+      <c r="F63" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>69</v>
@@ -3816,10 +4498,19 @@
       <c r="C64" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D64" t="s">
+        <v>79</v>
+      </c>
+      <c r="E64">
+        <v>2</v>
+      </c>
+      <c r="F64" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>69</v>
@@ -3827,10 +4518,19 @@
       <c r="C65" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D65" t="s">
+        <v>79</v>
+      </c>
+      <c r="E65">
+        <v>2</v>
+      </c>
+      <c r="F65" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>70</v>
@@ -3838,10 +4538,19 @@
       <c r="C66" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D66" t="s">
+        <v>79</v>
+      </c>
+      <c r="E66">
+        <v>2</v>
+      </c>
+      <c r="F66" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>70</v>
@@ -3849,10 +4558,19 @@
       <c r="C67" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D67" t="s">
+        <v>79</v>
+      </c>
+      <c r="E67">
+        <v>2</v>
+      </c>
+      <c r="F67" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>70</v>
@@ -3860,10 +4578,19 @@
       <c r="C68" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D68" t="s">
+        <v>79</v>
+      </c>
+      <c r="E68">
+        <v>2</v>
+      </c>
+      <c r="F68" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>71</v>
@@ -3871,10 +4598,19 @@
       <c r="C69" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D69" t="s">
+        <v>80</v>
+      </c>
+      <c r="E69">
+        <v>3</v>
+      </c>
+      <c r="F69" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>71</v>
@@ -3882,10 +4618,19 @@
       <c r="C70" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D70" t="s">
+        <v>80</v>
+      </c>
+      <c r="E70">
+        <v>3</v>
+      </c>
+      <c r="F70" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>71</v>
@@ -3893,36 +4638,51 @@
       <c r="C71" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D71" t="s">
+        <v>80</v>
+      </c>
+      <c r="E71">
+        <v>3</v>
+      </c>
+      <c r="F71" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>72</v>
       </c>
       <c r="C72" s="1"/>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D72" t="s">
+        <v>78</v>
+      </c>
+      <c r="E72">
+        <v>1</v>
+      </c>
+      <c r="F72" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>73</v>
       </c>
       <c r="C73" s="1"/>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C74" s="1"/>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C75" s="1"/>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C76" s="1"/>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C77" s="1"/>
+      <c r="D73" t="s">
+        <v>78</v>
+      </c>
+      <c r="E73">
+        <v>1</v>
+      </c>
+      <c r="F73" t="s">
+        <v>81</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Bases/Navegacao_Menu.xlsx
+++ b/Bases/Navegacao_Menu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djdan\Documents\GitHub\Dash-Upmat\Bases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E9933E-9F7D-4D71-8044-ECB802058851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF283FB0-36AD-4B60-BE88-A435C25C2B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="4" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="5" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
   </bookViews>
   <sheets>
     <sheet name="Olitef 2025" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="111">
   <si>
     <t>Ordem</t>
   </si>
@@ -154,9 +154,6 @@
     <t>Potencial de Conversão Inscrições 2025 - Part1</t>
   </si>
   <si>
-    <t>Migração Experience 2025 x 2026</t>
-  </si>
-  <si>
     <t>Migração de Plano 2025 x 2026</t>
   </si>
   <si>
@@ -229,12 +226,6 @@
     <t>Potencial de Conversão 2024 - Part2</t>
   </si>
   <si>
-    <t>Experience 2026</t>
-  </si>
-  <si>
-    <t>Engajamento Experience 2026</t>
-  </si>
-  <si>
     <t>Pedido de Medalhas 2025</t>
   </si>
   <si>
@@ -308,6 +299,84 @@
   </si>
   <si>
     <t>Migração Canguru Experience 2025 x 2026</t>
+  </si>
+  <si>
+    <t>1a</t>
+  </si>
+  <si>
+    <t>1b</t>
+  </si>
+  <si>
+    <t>1c</t>
+  </si>
+  <si>
+    <t>1d</t>
+  </si>
+  <si>
+    <t>1e</t>
+  </si>
+  <si>
+    <t>1f</t>
+  </si>
+  <si>
+    <t>1g</t>
+  </si>
+  <si>
+    <t>1h</t>
+  </si>
+  <si>
+    <t>1i</t>
+  </si>
+  <si>
+    <t>1j</t>
+  </si>
+  <si>
+    <t>1k</t>
+  </si>
+  <si>
+    <t>1l</t>
+  </si>
+  <si>
+    <t>1m</t>
+  </si>
+  <si>
+    <t>1n</t>
+  </si>
+  <si>
+    <t>1o</t>
+  </si>
+  <si>
+    <t>1p</t>
+  </si>
+  <si>
+    <t>1q</t>
+  </si>
+  <si>
+    <t>1r</t>
+  </si>
+  <si>
+    <t>1s</t>
+  </si>
+  <si>
+    <t>1t</t>
+  </si>
+  <si>
+    <t>1u</t>
+  </si>
+  <si>
+    <t>1v</t>
+  </si>
+  <si>
+    <t>1w</t>
+  </si>
+  <si>
+    <t>1y</t>
+  </si>
+  <si>
+    <t>1z</t>
+  </si>
+  <si>
+    <t>1x</t>
   </si>
 </sst>
 </file>
@@ -1361,7 +1430,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7F7F84F-51F4-4AA7-8488-D6CFB2C033F7}">
-  <dimension ref="A1:C87"/>
+  <dimension ref="A1:C74"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.5703125" bestFit="1" customWidth="1"/>
@@ -1420,7 +1489,7 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1464,7 +1533,7 @@
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1472,7 +1541,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>4</v>
@@ -1483,7 +1552,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>6</v>
@@ -1494,7 +1563,7 @@
         <v>3</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>5</v>
@@ -1505,10 +1574,10 @@
         <v>3</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1516,7 +1585,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>4</v>
@@ -1527,7 +1596,7 @@
         <v>4</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>6</v>
@@ -1538,7 +1607,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>5</v>
@@ -1549,10 +1618,10 @@
         <v>4</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -1560,7 +1629,7 @@
         <v>5</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>4</v>
@@ -1571,7 +1640,7 @@
         <v>5</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>5</v>
@@ -1582,7 +1651,7 @@
         <v>5</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>6</v>
@@ -1593,10 +1662,10 @@
         <v>5</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -1604,7 +1673,7 @@
         <v>6</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>4</v>
@@ -1615,7 +1684,7 @@
         <v>6</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>5</v>
@@ -1626,7 +1695,7 @@
         <v>6</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>6</v>
@@ -1637,10 +1706,10 @@
         <v>6</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -1648,7 +1717,7 @@
         <v>7</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>6</v>
@@ -1659,7 +1728,7 @@
         <v>7</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>5</v>
@@ -1670,7 +1739,7 @@
         <v>7</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>4</v>
@@ -1681,10 +1750,10 @@
         <v>7</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -1758,7 +1827,7 @@
         <v>10</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>5</v>
@@ -1769,7 +1838,7 @@
         <v>10</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>4</v>
@@ -1780,7 +1849,7 @@
         <v>10</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>6</v>
@@ -1791,7 +1860,7 @@
         <v>11</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>4</v>
@@ -1802,7 +1871,7 @@
         <v>11</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>6</v>
@@ -1813,7 +1882,7 @@
         <v>11</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>5</v>
@@ -1824,7 +1893,7 @@
         <v>12</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>4</v>
@@ -1835,7 +1904,7 @@
         <v>12</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>6</v>
@@ -1846,7 +1915,7 @@
         <v>12</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>5</v>
@@ -1857,7 +1926,7 @@
         <v>13</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>4</v>
@@ -1868,7 +1937,7 @@
         <v>13</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>6</v>
@@ -1879,7 +1948,7 @@
         <v>13</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>5</v>
@@ -1890,10 +1959,10 @@
         <v>14</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -1901,10 +1970,10 @@
         <v>14</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1912,10 +1981,10 @@
         <v>14</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1923,10 +1992,10 @@
         <v>15</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1934,10 +2003,10 @@
         <v>15</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1945,7 +2014,7 @@
         <v>15</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>4</v>
@@ -1956,7 +2025,7 @@
         <v>16</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>6</v>
@@ -1967,7 +2036,7 @@
         <v>16</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>5</v>
@@ -1978,7 +2047,7 @@
         <v>16</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>4</v>
@@ -1986,13 +2055,13 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C57" t="s">
-        <v>49</v>
+        <v>40</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -2000,10 +2069,10 @@
         <v>17</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -2011,7 +2080,7 @@
         <v>17</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>4</v>
@@ -2019,13 +2088,13 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -2033,10 +2102,10 @@
         <v>18</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -2044,7 +2113,7 @@
         <v>18</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>4</v>
@@ -2052,13 +2121,13 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -2066,10 +2135,10 @@
         <v>19</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -2077,21 +2146,21 @@
         <v>19</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -2099,40 +2168,40 @@
         <v>20</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>6</v>
@@ -2140,10 +2209,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>5</v>
@@ -2151,21 +2220,21 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>21</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>41</v>
+        <v>23</v>
+      </c>
+      <c r="B72" t="s">
+        <v>29</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>22</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>35</v>
+        <v>23</v>
+      </c>
+      <c r="B73" t="s">
+        <v>29</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>6</v>
@@ -2173,155 +2242,12 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>22</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>35</v>
+        <v>23</v>
+      </c>
+      <c r="B74" t="s">
+        <v>29</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="1">
-        <v>22</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="1">
-        <v>23</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="1">
-        <v>23</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="1">
-        <v>23</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="1">
-        <v>24</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="1">
-        <v>24</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="1">
-        <v>25</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="1">
-        <v>25</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="1">
-        <v>26</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="1">
-        <v>26</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="1">
-        <v>27</v>
-      </c>
-      <c r="B85" t="s">
-        <v>29</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="1">
-        <v>27</v>
-      </c>
-      <c r="B86" t="s">
-        <v>29</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="1">
-        <v>27</v>
-      </c>
-      <c r="B87" t="s">
-        <v>29</v>
-      </c>
-      <c r="C87" s="1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2497,7 +2423,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>4</v>
@@ -2508,7 +2434,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>6</v>
@@ -2519,7 +2445,7 @@
         <v>3</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>5</v>
@@ -2530,7 +2456,7 @@
         <v>4</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>19</v>
@@ -2541,7 +2467,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>6</v>
@@ -2552,7 +2478,7 @@
         <v>5</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>6</v>
@@ -2563,7 +2489,7 @@
         <v>5</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>4</v>
@@ -2574,7 +2500,7 @@
         <v>5</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>5</v>
@@ -2585,7 +2511,7 @@
         <v>6</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>19</v>
@@ -2596,7 +2522,7 @@
         <v>6</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>4</v>
@@ -2607,7 +2533,7 @@
         <v>6</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>5</v>
@@ -2618,7 +2544,7 @@
         <v>6</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>6</v>
@@ -2794,7 +2720,7 @@
         <v>13</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>6</v>
@@ -2816,7 +2742,7 @@
         <v>15</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>19</v>
@@ -2827,7 +2753,7 @@
         <v>15</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>4</v>
@@ -2838,7 +2764,7 @@
         <v>15</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>5</v>
@@ -2849,7 +2775,7 @@
         <v>15</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>6</v>
@@ -2860,7 +2786,7 @@
         <v>16</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>19</v>
@@ -2871,7 +2797,7 @@
         <v>16</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>4</v>
@@ -2882,7 +2808,7 @@
         <v>16</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>5</v>
@@ -2893,7 +2819,7 @@
         <v>16</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>6</v>
@@ -2904,7 +2830,7 @@
         <v>17</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>6</v>
@@ -2915,7 +2841,7 @@
         <v>18</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>6</v>
@@ -2926,7 +2852,7 @@
         <v>19</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>6</v>
@@ -2948,7 +2874,7 @@
         <v>21</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>6</v>
@@ -2959,7 +2885,7 @@
         <v>22</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>6</v>
@@ -2970,7 +2896,7 @@
         <v>23</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>6</v>
@@ -3007,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
@@ -3018,7 +2944,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>6</v>
@@ -3029,7 +2955,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -3040,10 +2966,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -3051,7 +2977,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>5</v>
@@ -3062,7 +2988,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>6</v>
@@ -3073,7 +2999,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>4</v>
@@ -3084,10 +3010,10 @@
         <v>2</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -3095,7 +3021,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>5</v>
@@ -3106,7 +3032,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>6</v>
@@ -3117,7 +3043,7 @@
         <v>3</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>4</v>
@@ -3128,10 +3054,10 @@
         <v>3</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -3139,7 +3065,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>6</v>
@@ -3150,7 +3076,7 @@
         <v>4</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>5</v>
@@ -3161,7 +3087,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>4</v>
@@ -3172,10 +3098,10 @@
         <v>4</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -3183,7 +3109,7 @@
         <v>5</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>6</v>
@@ -3194,7 +3120,7 @@
         <v>5</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>4</v>
@@ -3205,7 +3131,7 @@
         <v>5</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>5</v>
@@ -3216,10 +3142,10 @@
         <v>5</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" t="s">
         <v>48</v>
-      </c>
-      <c r="C21" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -3229,7 +3155,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AD31D2E-82F9-4A53-8E31-D57E1126423D}">
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.5703125" bestFit="1" customWidth="1"/>
@@ -3249,18 +3175,18 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
+      <c r="A2" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>25</v>
@@ -3269,18 +3195,18 @@
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>1</v>
+      <c r="A3" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>25</v>
@@ -3289,18 +3215,18 @@
         <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>1</v>
+      <c r="A4" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>25</v>
@@ -3309,38 +3235,38 @@
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>1</v>
+      <c r="A5" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>2</v>
+      <c r="A6" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>26</v>
@@ -3349,18 +3275,18 @@
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>2</v>
+      <c r="A7" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>26</v>
@@ -3369,18 +3295,18 @@
         <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>2</v>
+      <c r="A8" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>26</v>
@@ -3389,358 +3315,358 @@
         <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>2</v>
+      <c r="A9" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>3</v>
+      <c r="A10" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>3</v>
+      <c r="A11" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>3</v>
+      <c r="A12" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>3</v>
+      <c r="A13" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>4</v>
+      <c r="A14" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>4</v>
+      <c r="A15" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>4</v>
+      <c r="A16" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D16" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E16">
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <v>4</v>
+      <c r="A17" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E17">
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>5</v>
+      <c r="A18" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>5</v>
+      <c r="A19" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D19" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E19">
         <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>5</v>
+      <c r="A20" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D20" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>5</v>
+      <c r="A21" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D21" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>6</v>
+      <c r="A22" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D22" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>6</v>
+      <c r="A23" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D23" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <v>6</v>
+      <c r="A24" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D24" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>6</v>
+      <c r="A25" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D25" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <v>7</v>
+      <c r="A26" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>30</v>
@@ -3749,18 +3675,18 @@
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E26">
         <v>2</v>
       </c>
       <c r="F26" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
-        <v>7</v>
+      <c r="A27" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>30</v>
@@ -3769,18 +3695,18 @@
         <v>4</v>
       </c>
       <c r="D27" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E27">
         <v>2</v>
       </c>
       <c r="F27" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
-        <v>7</v>
+      <c r="A28" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>30</v>
@@ -3789,18 +3715,18 @@
         <v>6</v>
       </c>
       <c r="D28" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E28">
         <v>2</v>
       </c>
       <c r="F28" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
-        <v>8</v>
+      <c r="A29" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>28</v>
@@ -3809,18 +3735,18 @@
         <v>5</v>
       </c>
       <c r="D29" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E29">
         <v>2</v>
       </c>
       <c r="F29" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
-        <v>8</v>
+      <c r="A30" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>28</v>
@@ -3829,18 +3755,18 @@
         <v>4</v>
       </c>
       <c r="D30" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E30">
         <v>2</v>
       </c>
       <c r="F30" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
-        <v>8</v>
+      <c r="A31" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>28</v>
@@ -3849,839 +3775,1111 @@
         <v>6</v>
       </c>
       <c r="D31" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E31">
         <v>2</v>
       </c>
       <c r="F31" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
-        <v>9</v>
+      <c r="A32" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C32" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="D32" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E32">
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
-        <v>10</v>
-      </c>
-      <c r="B33" t="s">
+      <c r="A33" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" t="s">
+        <v>75</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D34" t="s">
+        <v>75</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35" t="s">
+        <v>48</v>
+      </c>
+      <c r="D35" t="s">
+        <v>75</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+      <c r="F35" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B36" t="s">
         <v>29</v>
       </c>
-      <c r="C33" s="1"/>
-      <c r="D33" t="s">
+      <c r="C36" s="1"/>
+      <c r="D36" t="s">
+        <v>76</v>
+      </c>
+      <c r="E36">
+        <v>2</v>
+      </c>
+      <c r="F36" t="s">
         <v>79</v>
       </c>
-      <c r="E33">
-        <v>2</v>
-      </c>
-      <c r="F33" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
-        <v>11</v>
-      </c>
-      <c r="B34" s="1" t="s">
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D34" t="s">
-        <v>78</v>
-      </c>
-      <c r="E34">
-        <v>1</v>
-      </c>
-      <c r="F34" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
-        <v>11</v>
-      </c>
-      <c r="B35" s="1" t="s">
+      <c r="C37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" t="s">
+        <v>75</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+      <c r="F37" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D35" t="s">
-        <v>78</v>
-      </c>
-      <c r="E35">
-        <v>1</v>
-      </c>
-      <c r="F35" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
-        <v>11</v>
-      </c>
-      <c r="B36" s="1" t="s">
+      <c r="C38" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D38" t="s">
+        <v>75</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D36" t="s">
-        <v>78</v>
-      </c>
-      <c r="E36">
-        <v>1</v>
-      </c>
-      <c r="F36" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
-        <v>12</v>
-      </c>
-      <c r="B37" s="1" t="s">
+      <c r="C39" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D39" t="s">
+        <v>75</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+      <c r="F39" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C40" t="s">
+        <v>48</v>
+      </c>
+      <c r="D40" t="s">
+        <v>75</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+      <c r="F40" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D37" t="s">
-        <v>78</v>
-      </c>
-      <c r="E37">
-        <v>1</v>
-      </c>
-      <c r="F37" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
-        <v>12</v>
-      </c>
-      <c r="B38" s="1" t="s">
+      <c r="C41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41" t="s">
+        <v>75</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+      <c r="F41" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D38" t="s">
-        <v>78</v>
-      </c>
-      <c r="E38">
-        <v>1</v>
-      </c>
-      <c r="F38" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
-        <v>12</v>
-      </c>
-      <c r="B39" s="1" t="s">
+      <c r="C42" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42" t="s">
+        <v>75</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+      <c r="F42" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D39" t="s">
-        <v>78</v>
-      </c>
-      <c r="E39">
-        <v>1</v>
-      </c>
-      <c r="F39" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
-        <v>13</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D40" t="s">
-        <v>78</v>
-      </c>
-      <c r="E40">
-        <v>1</v>
-      </c>
-      <c r="F40" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="1">
-        <v>13</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D41" t="s">
-        <v>78</v>
-      </c>
-      <c r="E41">
-        <v>1</v>
-      </c>
-      <c r="F41" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="1">
-        <v>13</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D42" t="s">
-        <v>78</v>
-      </c>
-      <c r="E42">
-        <v>1</v>
-      </c>
-      <c r="F42" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="1">
-        <v>14</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="C43" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D43" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="1">
-        <v>14</v>
+      <c r="A44" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="C44" t="s">
+        <v>48</v>
       </c>
       <c r="D44" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="1">
-        <v>14</v>
+      <c r="A45" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D45" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F45" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="1">
-        <v>15</v>
+      <c r="A46" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D46" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="1">
-        <v>15</v>
+      <c r="A47" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D47" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="1">
-        <v>15</v>
+      <c r="A48" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D48" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E48">
         <v>2</v>
       </c>
       <c r="F48" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="1">
-        <v>16</v>
+      <c r="A49" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="B49" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D49" t="s">
+        <v>76</v>
+      </c>
+      <c r="E49">
+        <v>2</v>
+      </c>
+      <c r="F49" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D50" t="s">
+        <v>76</v>
+      </c>
+      <c r="E50">
+        <v>2</v>
+      </c>
+      <c r="F50" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D51" t="s">
+        <v>76</v>
+      </c>
+      <c r="E51">
+        <v>2</v>
+      </c>
+      <c r="F51" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D52" t="s">
+        <v>76</v>
+      </c>
+      <c r="E52">
+        <v>2</v>
+      </c>
+      <c r="F52" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D53" t="s">
+        <v>76</v>
+      </c>
+      <c r="E53">
+        <v>2</v>
+      </c>
+      <c r="F53" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D54" t="s">
+        <v>77</v>
+      </c>
+      <c r="E54">
+        <v>3</v>
+      </c>
+      <c r="F54" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D55" t="s">
+        <v>77</v>
+      </c>
+      <c r="E55">
+        <v>3</v>
+      </c>
+      <c r="F55" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D56" t="s">
+        <v>77</v>
+      </c>
+      <c r="E56">
+        <v>3</v>
+      </c>
+      <c r="F56" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D57" t="s">
+        <v>75</v>
+      </c>
+      <c r="E57">
+        <v>1</v>
+      </c>
+      <c r="F57" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D58" t="s">
+        <v>75</v>
+      </c>
+      <c r="E58">
+        <v>1</v>
+      </c>
+      <c r="F58" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D59" t="s">
+        <v>75</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+      <c r="F59" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D60" t="s">
+        <v>75</v>
+      </c>
+      <c r="E60">
+        <v>1</v>
+      </c>
+      <c r="F60" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D61" t="s">
+        <v>75</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
+      <c r="F61" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D62" t="s">
+        <v>75</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+      <c r="F62" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D49" t="s">
+      <c r="C63" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D63" t="s">
+        <v>75</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+      <c r="F63" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D64" t="s">
+        <v>75</v>
+      </c>
+      <c r="E64">
+        <v>1</v>
+      </c>
+      <c r="F64" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D65" t="s">
+        <v>75</v>
+      </c>
+      <c r="E65">
+        <v>1</v>
+      </c>
+      <c r="F65" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D66" t="s">
+        <v>75</v>
+      </c>
+      <c r="E66">
+        <v>1</v>
+      </c>
+      <c r="F66" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D67" t="s">
+        <v>75</v>
+      </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
+      <c r="F67" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D68" t="s">
+        <v>75</v>
+      </c>
+      <c r="E68">
+        <v>1</v>
+      </c>
+      <c r="F68" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D69" t="s">
+        <v>75</v>
+      </c>
+      <c r="E69">
+        <v>1</v>
+      </c>
+      <c r="F69" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D70" t="s">
+        <v>75</v>
+      </c>
+      <c r="E70">
+        <v>1</v>
+      </c>
+      <c r="F70" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D71" t="s">
+        <v>75</v>
+      </c>
+      <c r="E71">
+        <v>1</v>
+      </c>
+      <c r="F71" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D72" t="s">
+        <v>76</v>
+      </c>
+      <c r="E72">
+        <v>2</v>
+      </c>
+      <c r="F72" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D73" t="s">
+        <v>76</v>
+      </c>
+      <c r="E73">
+        <v>2</v>
+      </c>
+      <c r="F73" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D74" t="s">
+        <v>76</v>
+      </c>
+      <c r="E74">
+        <v>2</v>
+      </c>
+      <c r="F74" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D75" t="s">
+        <v>76</v>
+      </c>
+      <c r="E75">
+        <v>2</v>
+      </c>
+      <c r="F75" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D76" t="s">
+        <v>76</v>
+      </c>
+      <c r="E76">
+        <v>2</v>
+      </c>
+      <c r="F76" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D77" t="s">
+        <v>76</v>
+      </c>
+      <c r="E77">
+        <v>2</v>
+      </c>
+      <c r="F77" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D78" t="s">
+        <v>77</v>
+      </c>
+      <c r="E78">
+        <v>3</v>
+      </c>
+      <c r="F78" t="s">
         <v>80</v>
       </c>
-      <c r="E49">
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D79" t="s">
+        <v>77</v>
+      </c>
+      <c r="E79">
         <v>3</v>
       </c>
-      <c r="F49" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="1">
-        <v>16</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="F79" t="s">
         <v>80</v>
       </c>
-      <c r="E50">
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D80" t="s">
+        <v>77</v>
+      </c>
+      <c r="E80">
         <v>3</v>
       </c>
-      <c r="F50" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="1">
-        <v>16</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D51" t="s">
+      <c r="F80" t="s">
         <v>80</v>
       </c>
-      <c r="E51">
-        <v>3</v>
-      </c>
-      <c r="F51" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="1">
-        <v>17</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D52" t="s">
-        <v>78</v>
-      </c>
-      <c r="E52">
-        <v>1</v>
-      </c>
-      <c r="F52" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="1">
-        <v>18</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D53" t="s">
-        <v>78</v>
-      </c>
-      <c r="E53">
-        <v>1</v>
-      </c>
-      <c r="F53" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="1">
-        <v>19</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D54" t="s">
-        <v>78</v>
-      </c>
-      <c r="E54">
-        <v>1</v>
-      </c>
-      <c r="F54" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="1">
-        <v>19</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D55" t="s">
-        <v>78</v>
-      </c>
-      <c r="E55">
-        <v>1</v>
-      </c>
-      <c r="F55" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="1">
-        <v>19</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D56" t="s">
-        <v>78</v>
-      </c>
-      <c r="E56">
-        <v>1</v>
-      </c>
-      <c r="F56" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="1">
-        <v>20</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D57" t="s">
-        <v>78</v>
-      </c>
-      <c r="E57">
-        <v>1</v>
-      </c>
-      <c r="F57" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="1">
-        <v>20</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D58" t="s">
-        <v>78</v>
-      </c>
-      <c r="E58">
-        <v>1</v>
-      </c>
-      <c r="F58" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="1">
-        <v>20</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D59" t="s">
-        <v>78</v>
-      </c>
-      <c r="E59">
-        <v>1</v>
-      </c>
-      <c r="F59" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="1">
-        <v>21</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D60" t="s">
-        <v>78</v>
-      </c>
-      <c r="E60">
-        <v>1</v>
-      </c>
-      <c r="F60" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="1">
-        <v>21</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D61" t="s">
-        <v>78</v>
-      </c>
-      <c r="E61">
-        <v>1</v>
-      </c>
-      <c r="F61" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="1">
-        <v>21</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D62" t="s">
-        <v>78</v>
-      </c>
-      <c r="E62">
-        <v>1</v>
-      </c>
-      <c r="F62" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="1">
-        <v>22</v>
-      </c>
-      <c r="B63" s="1" t="s">
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C63" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D63" t="s">
-        <v>79</v>
-      </c>
-      <c r="E63">
-        <v>2</v>
-      </c>
-      <c r="F63" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="1">
-        <v>22</v>
-      </c>
-      <c r="B64" s="1" t="s">
+      <c r="C81" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D81" t="s">
+        <v>75</v>
+      </c>
+      <c r="E81">
+        <v>1</v>
+      </c>
+      <c r="F81" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C64" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D64" t="s">
-        <v>79</v>
-      </c>
-      <c r="E64">
-        <v>2</v>
-      </c>
-      <c r="F64" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="1">
-        <v>22</v>
-      </c>
-      <c r="B65" s="1" t="s">
+      <c r="C82" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D82" t="s">
+        <v>75</v>
+      </c>
+      <c r="E82">
+        <v>1</v>
+      </c>
+      <c r="F82" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D65" t="s">
-        <v>79</v>
-      </c>
-      <c r="E65">
-        <v>2</v>
-      </c>
-      <c r="F65" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="1">
-        <v>23</v>
-      </c>
-      <c r="B66" s="1" t="s">
+      <c r="C83" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D83" t="s">
+        <v>75</v>
+      </c>
+      <c r="E83">
+        <v>1</v>
+      </c>
+      <c r="F83" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D66" t="s">
-        <v>79</v>
-      </c>
-      <c r="E66">
-        <v>2</v>
-      </c>
-      <c r="F66" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="1">
-        <v>23</v>
-      </c>
-      <c r="B67" s="1" t="s">
+      <c r="C84" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D84" t="s">
+        <v>75</v>
+      </c>
+      <c r="E84">
+        <v>1</v>
+      </c>
+      <c r="F84" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C67" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D67" t="s">
-        <v>79</v>
-      </c>
-      <c r="E67">
-        <v>2</v>
-      </c>
-      <c r="F67" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="1">
-        <v>23</v>
-      </c>
-      <c r="B68" s="1" t="s">
+      <c r="C85" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D85" t="s">
+        <v>75</v>
+      </c>
+      <c r="E85">
+        <v>1</v>
+      </c>
+      <c r="F85" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C68" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D68" t="s">
-        <v>79</v>
-      </c>
-      <c r="E68">
-        <v>2</v>
-      </c>
-      <c r="F68" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="1">
-        <v>24</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D69" t="s">
-        <v>80</v>
-      </c>
-      <c r="E69">
-        <v>3</v>
-      </c>
-      <c r="F69" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="1">
-        <v>24</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D70" t="s">
-        <v>80</v>
-      </c>
-      <c r="E70">
-        <v>3</v>
-      </c>
-      <c r="F70" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="1">
-        <v>24</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D71" t="s">
-        <v>80</v>
-      </c>
-      <c r="E71">
-        <v>3</v>
-      </c>
-      <c r="F71" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="1">
-        <v>25</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C72" s="1"/>
-      <c r="D72" t="s">
-        <v>78</v>
-      </c>
-      <c r="E72">
-        <v>1</v>
-      </c>
-      <c r="F72" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="1">
-        <v>26</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C73" s="1"/>
-      <c r="D73" t="s">
-        <v>78</v>
-      </c>
-      <c r="E73">
-        <v>1</v>
-      </c>
-      <c r="F73" t="s">
-        <v>81</v>
+      <c r="C86" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D86" t="s">
+        <v>75</v>
+      </c>
+      <c r="E86">
+        <v>1</v>
+      </c>
+      <c r="F86" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/Bases/Navegacao_Menu.xlsx
+++ b/Bases/Navegacao_Menu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djdan\Documents\GitHub\Dash-Upmat\Bases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF283FB0-36AD-4B60-BE88-A435C25C2B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D20336CC-2CBE-4EB9-98B5-E5A082C7D971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="5" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="4" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
   </bookViews>
   <sheets>
     <sheet name="Olitef 2025" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="112">
   <si>
     <t>Ordem</t>
   </si>
@@ -377,6 +377,9 @@
   </si>
   <si>
     <t>1x</t>
+  </si>
+  <si>
+    <t>Bebras Experience 2026</t>
   </si>
 </sst>
 </file>
@@ -2910,7 +2913,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FA0C564-8652-48EB-AFAF-28B449B9D62C}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.5703125" bestFit="1" customWidth="1"/>
@@ -3145,6 +3148,50 @@
         <v>47</v>
       </c>
       <c r="C21" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>6</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>6</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>6</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>6</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C25" t="s">
         <v>48</v>
       </c>
     </row>

--- a/Bases/Navegacao_Menu.xlsx
+++ b/Bases/Navegacao_Menu.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djdan\Documents\GitHub\Dash-Upmat\Bases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D20336CC-2CBE-4EB9-98B5-E5A082C7D971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33BB8D81-8499-441D-9730-CF83CBBEF8A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="4" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
+    <workbookView xWindow="23880" yWindow="855" windowWidth="20640" windowHeight="11040" firstSheet="1" activeTab="5" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
   </bookViews>
   <sheets>
     <sheet name="Olitef 2025" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="111">
   <si>
     <t>Ordem</t>
   </si>
@@ -326,9 +326,6 @@
   </si>
   <si>
     <t>1i</t>
-  </si>
-  <si>
-    <t>1j</t>
   </si>
   <si>
     <t>1k</t>
@@ -3156,7 +3153,7 @@
         <v>6</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>6</v>
@@ -3167,7 +3164,7 @@
         <v>6</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>4</v>
@@ -3178,7 +3175,7 @@
         <v>6</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>5</v>
@@ -3189,7 +3186,7 @@
         <v>6</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C25" t="s">
         <v>48</v>
@@ -3202,13 +3199,15 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AD31D2E-82F9-4A53-8E31-D57E1126423D}">
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="42.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="2" max="2" width="42.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3241,13 +3240,13 @@
       <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="D2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3261,13 +3260,13 @@
       <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="D3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3281,13 +3280,13 @@
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="D4" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3298,16 +3297,16 @@
       <c r="B5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="D5" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3321,13 +3320,13 @@
       <c r="C6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D6" t="s">
-        <v>75</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="D6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3341,13 +3340,13 @@
       <c r="C7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="D7" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3361,13 +3360,13 @@
       <c r="C8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="D8" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3378,16 +3377,16 @@
       <c r="B9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="D9" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3401,13 +3400,13 @@
       <c r="C10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D10" t="s">
-        <v>75</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="D10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3421,13 +3420,13 @@
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="D11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3441,13 +3440,13 @@
       <c r="C12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="D12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3458,16 +3457,16 @@
       <c r="B13" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="D13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3481,13 +3480,13 @@
       <c r="C14" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D14" t="s">
-        <v>75</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="D14" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3501,13 +3500,13 @@
       <c r="C15" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D15" t="s">
-        <v>75</v>
-      </c>
-      <c r="E15">
-        <v>1</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="D15" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3521,13 +3520,13 @@
       <c r="C16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D16" t="s">
-        <v>75</v>
-      </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="D16" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" s="1">
+        <v>1</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3538,16 +3537,16 @@
       <c r="B17" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D17" t="s">
-        <v>75</v>
-      </c>
-      <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="D17" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3561,13 +3560,13 @@
       <c r="C18" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D18" t="s">
-        <v>75</v>
-      </c>
-      <c r="E18">
-        <v>1</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="D18" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="1">
+        <v>1</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3581,13 +3580,13 @@
       <c r="C19" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D19" t="s">
-        <v>75</v>
-      </c>
-      <c r="E19">
-        <v>1</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="D19" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3601,13 +3600,13 @@
       <c r="C20" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D20" t="s">
-        <v>75</v>
-      </c>
-      <c r="E20">
-        <v>1</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="D20" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" s="1">
+        <v>1</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3618,16 +3617,16 @@
       <c r="B21" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D21" t="s">
-        <v>75</v>
-      </c>
-      <c r="E21">
-        <v>1</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="D21" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="1">
+        <v>1</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3641,13 +3640,13 @@
       <c r="C22" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="D22" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="1">
+        <v>1</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3661,13 +3660,13 @@
       <c r="C23" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D23" t="s">
-        <v>75</v>
-      </c>
-      <c r="E23">
-        <v>1</v>
-      </c>
-      <c r="F23" t="s">
+      <c r="D23" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3681,13 +3680,13 @@
       <c r="C24" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D24" t="s">
-        <v>75</v>
-      </c>
-      <c r="E24">
-        <v>1</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="D24" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3698,16 +3697,16 @@
       <c r="B25" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D25" t="s">
-        <v>75</v>
-      </c>
-      <c r="E25">
-        <v>1</v>
-      </c>
-      <c r="F25" t="s">
+      <c r="D25" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E25" s="1">
+        <v>1</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3716,18 +3715,18 @@
         <v>91</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D26" t="s">
-        <v>76</v>
-      </c>
-      <c r="E26">
-        <v>2</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="D26" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>79</v>
       </c>
     </row>
@@ -3736,18 +3735,18 @@
         <v>91</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D27" t="s">
-        <v>76</v>
-      </c>
-      <c r="E27">
-        <v>2</v>
-      </c>
-      <c r="F27" t="s">
+      <c r="D27" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>79</v>
       </c>
     </row>
@@ -3756,38 +3755,38 @@
         <v>91</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D28" t="s">
-        <v>76</v>
-      </c>
-      <c r="E28">
-        <v>2</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="D28" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E28" s="1">
+        <v>1</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D29" t="s">
-        <v>76</v>
-      </c>
-      <c r="E29">
-        <v>2</v>
-      </c>
-      <c r="F29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E29" s="1">
+        <v>1</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>79</v>
       </c>
     </row>
@@ -3796,18 +3795,18 @@
         <v>92</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D30" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="1">
         <v>2</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="1" t="s">
         <v>79</v>
       </c>
     </row>
@@ -3816,39 +3815,39 @@
         <v>92</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="1">
         <v>2</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="1" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D32" t="s">
-        <v>75</v>
-      </c>
-      <c r="E32">
-        <v>1</v>
-      </c>
-      <c r="F32" t="s">
-        <v>78</v>
+        <v>6</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E32" s="1">
+        <v>2</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -3856,18 +3855,18 @@
         <v>93</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D33" t="s">
-        <v>75</v>
-      </c>
-      <c r="E33">
-        <v>1</v>
-      </c>
-      <c r="F33" t="s">
+        <v>4</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E33" s="1">
+        <v>2</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3876,18 +3875,18 @@
         <v>93</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D34" t="s">
-        <v>75</v>
-      </c>
-      <c r="E34">
-        <v>1</v>
-      </c>
-      <c r="F34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E34" s="1">
+        <v>2</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3896,18 +3895,18 @@
         <v>93</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C35" t="s">
-        <v>48</v>
-      </c>
-      <c r="D35" t="s">
-        <v>75</v>
-      </c>
-      <c r="E35">
-        <v>1</v>
-      </c>
-      <c r="F35" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E35" s="1">
+        <v>2</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3915,77 +3914,79 @@
       <c r="A36" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B36" t="s">
-        <v>29</v>
-      </c>
-      <c r="C36" s="1"/>
-      <c r="D36" t="s">
-        <v>76</v>
-      </c>
-      <c r="E36">
-        <v>2</v>
-      </c>
-      <c r="F36" t="s">
-        <v>79</v>
+      <c r="B36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E36" s="1">
+        <v>1</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D37" t="s">
-        <v>75</v>
-      </c>
-      <c r="E37">
-        <v>1</v>
-      </c>
-      <c r="F37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E37" s="1">
+        <v>1</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D38" t="s">
-        <v>75</v>
-      </c>
-      <c r="E38">
-        <v>1</v>
-      </c>
-      <c r="F38" t="s">
+        <v>4</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E38" s="1">
+        <v>1</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D39" t="s">
-        <v>75</v>
-      </c>
-      <c r="E39">
-        <v>1</v>
-      </c>
-      <c r="F39" t="s">
+        <v>48</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E39" s="1">
+        <v>1</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3994,78 +3995,78 @@
         <v>95</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C40" t="s">
-        <v>48</v>
-      </c>
-      <c r="D40" t="s">
-        <v>75</v>
-      </c>
-      <c r="E40">
-        <v>1</v>
-      </c>
-      <c r="F40" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E40" s="1">
+        <v>1</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D41" t="s">
-        <v>75</v>
-      </c>
-      <c r="E41">
-        <v>1</v>
-      </c>
-      <c r="F41" t="s">
+        <v>5</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E41" s="1">
+        <v>1</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D42" t="s">
-        <v>75</v>
-      </c>
-      <c r="E42">
-        <v>1</v>
-      </c>
-      <c r="F42" t="s">
+        <v>4</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E42" s="1">
+        <v>1</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D43" t="s">
-        <v>75</v>
-      </c>
-      <c r="E43">
-        <v>1</v>
-      </c>
-      <c r="F43" t="s">
+        <v>48</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E43" s="1">
+        <v>1</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -4074,58 +4075,58 @@
         <v>96</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" t="s">
-        <v>48</v>
-      </c>
-      <c r="D44" t="s">
-        <v>75</v>
-      </c>
-      <c r="E44">
-        <v>1</v>
-      </c>
-      <c r="F44" t="s">
+        <v>40</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E44" s="1">
+        <v>1</v>
+      </c>
+      <c r="F44" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D45" t="s">
-        <v>75</v>
-      </c>
-      <c r="E45">
-        <v>1</v>
-      </c>
-      <c r="F45" t="s">
+        <v>5</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E45" s="1">
+        <v>1</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D46" t="s">
-        <v>75</v>
-      </c>
-      <c r="E46">
-        <v>1</v>
-      </c>
-      <c r="F46" t="s">
+        <v>4</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E46" s="1">
+        <v>1</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -4134,58 +4135,58 @@
         <v>97</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D47" t="s">
-        <v>75</v>
-      </c>
-      <c r="E47">
-        <v>1</v>
-      </c>
-      <c r="F47" t="s">
-        <v>78</v>
+        <v>6</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E47" s="1">
+        <v>2</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D48" t="s">
+        <v>5</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E48">
+      <c r="E48" s="1">
         <v>2</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F48" s="1" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D49" t="s">
+        <v>4</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E49">
+      <c r="E49" s="1">
         <v>2</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F49" s="1" t="s">
         <v>79</v>
       </c>
     </row>
@@ -4194,58 +4195,58 @@
         <v>98</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D50" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E50">
+      <c r="E50" s="1">
         <v>2</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F50" s="1" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>61</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D51" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E51">
+      <c r="E51" s="1">
         <v>2</v>
       </c>
-      <c r="F51" t="s">
+      <c r="F51" s="1" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>61</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D52" t="s">
+        <v>4</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E52">
+      <c r="E52" s="1">
         <v>2</v>
       </c>
-      <c r="F52" t="s">
+      <c r="F52" s="1" t="s">
         <v>79</v>
       </c>
     </row>
@@ -4254,58 +4255,58 @@
         <v>99</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D53" t="s">
-        <v>76</v>
-      </c>
-      <c r="E53">
-        <v>2</v>
-      </c>
-      <c r="F53" t="s">
-        <v>79</v>
+        <v>6</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E53" s="1">
+        <v>3</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>60</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D54" t="s">
+        <v>5</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E54">
+      <c r="E54" s="1">
         <v>3</v>
       </c>
-      <c r="F54" t="s">
+      <c r="F54" s="1" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>60</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D55" t="s">
+        <v>4</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E55">
+      <c r="E55" s="1">
         <v>3</v>
       </c>
-      <c r="F55" t="s">
+      <c r="F55" s="1" t="s">
         <v>80</v>
       </c>
     </row>
@@ -4314,58 +4315,58 @@
         <v>100</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D56" t="s">
-        <v>77</v>
-      </c>
-      <c r="E56">
-        <v>3</v>
-      </c>
-      <c r="F56" t="s">
-        <v>80</v>
+        <v>6</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E56" s="1">
+        <v>1</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D57" t="s">
-        <v>75</v>
-      </c>
-      <c r="E57">
-        <v>1</v>
-      </c>
-      <c r="F57" t="s">
+        <v>5</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E57" s="1">
+        <v>1</v>
+      </c>
+      <c r="F57" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D58" t="s">
-        <v>75</v>
-      </c>
-      <c r="E58">
-        <v>1</v>
-      </c>
-      <c r="F58" t="s">
+        <v>4</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E58" s="1">
+        <v>1</v>
+      </c>
+      <c r="F58" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -4374,58 +4375,58 @@
         <v>101</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D59" t="s">
-        <v>75</v>
-      </c>
-      <c r="E59">
-        <v>1</v>
-      </c>
-      <c r="F59" t="s">
+        <v>6</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E59" s="1">
+        <v>1</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>34</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D60" t="s">
-        <v>75</v>
-      </c>
-      <c r="E60">
-        <v>1</v>
-      </c>
-      <c r="F60" t="s">
+        <v>5</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E60" s="1">
+        <v>1</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>34</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D61" t="s">
-        <v>75</v>
-      </c>
-      <c r="E61">
-        <v>1</v>
-      </c>
-      <c r="F61" t="s">
+        <v>4</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E61" s="1">
+        <v>1</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -4434,58 +4435,58 @@
         <v>102</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D62" t="s">
-        <v>75</v>
-      </c>
-      <c r="E62">
-        <v>1</v>
-      </c>
-      <c r="F62" t="s">
+        <v>6</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E62" s="1">
+        <v>1</v>
+      </c>
+      <c r="F62" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D63" t="s">
-        <v>75</v>
-      </c>
-      <c r="E63">
-        <v>1</v>
-      </c>
-      <c r="F63" t="s">
+        <v>5</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E63" s="1">
+        <v>1</v>
+      </c>
+      <c r="F63" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D64" t="s">
-        <v>75</v>
-      </c>
-      <c r="E64">
-        <v>1</v>
-      </c>
-      <c r="F64" t="s">
+        <v>4</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E64" s="1">
+        <v>1</v>
+      </c>
+      <c r="F64" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -4494,58 +4495,58 @@
         <v>103</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D65" t="s">
-        <v>75</v>
-      </c>
-      <c r="E65">
-        <v>1</v>
-      </c>
-      <c r="F65" t="s">
+        <v>6</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E65" s="1">
+        <v>1</v>
+      </c>
+      <c r="F65" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>64</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D66" t="s">
-        <v>75</v>
-      </c>
-      <c r="E66">
-        <v>1</v>
-      </c>
-      <c r="F66" t="s">
+        <v>5</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E66" s="1">
+        <v>1</v>
+      </c>
+      <c r="F66" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>64</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D67" t="s">
-        <v>75</v>
-      </c>
-      <c r="E67">
-        <v>1</v>
-      </c>
-      <c r="F67" t="s">
+        <v>4</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E67" s="1">
+        <v>1</v>
+      </c>
+      <c r="F67" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -4554,58 +4555,58 @@
         <v>104</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D68" t="s">
-        <v>75</v>
-      </c>
-      <c r="E68">
-        <v>1</v>
-      </c>
-      <c r="F68" t="s">
+        <v>6</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E68" s="1">
+        <v>1</v>
+      </c>
+      <c r="F68" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D69" t="s">
-        <v>75</v>
-      </c>
-      <c r="E69">
-        <v>1</v>
-      </c>
-      <c r="F69" t="s">
+        <v>5</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E69" s="1">
+        <v>1</v>
+      </c>
+      <c r="F69" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D70" t="s">
-        <v>75</v>
-      </c>
-      <c r="E70">
-        <v>1</v>
-      </c>
-      <c r="F70" t="s">
+        <v>4</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E70" s="1">
+        <v>1</v>
+      </c>
+      <c r="F70" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -4614,58 +4615,58 @@
         <v>105</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D71" t="s">
-        <v>75</v>
-      </c>
-      <c r="E71">
-        <v>1</v>
-      </c>
-      <c r="F71" t="s">
-        <v>78</v>
+        <v>6</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E71" s="1">
+        <v>2</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>66</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D72" t="s">
+        <v>5</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E72">
+      <c r="E72" s="1">
         <v>2</v>
       </c>
-      <c r="F72" t="s">
+      <c r="F72" s="1" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>66</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D73" t="s">
+        <v>4</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E73">
+      <c r="E73" s="1">
         <v>2</v>
       </c>
-      <c r="F73" t="s">
+      <c r="F73" s="1" t="s">
         <v>79</v>
       </c>
     </row>
@@ -4674,178 +4675,178 @@
         <v>106</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D74" t="s">
+        <v>6</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E74">
+      <c r="E74" s="1">
         <v>2</v>
       </c>
-      <c r="F74" t="s">
+      <c r="F74" s="1" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>67</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D75" t="s">
+        <v>5</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E75">
+      <c r="E75" s="1">
         <v>2</v>
       </c>
-      <c r="F75" t="s">
+      <c r="F75" s="1" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D76" t="s">
+        <v>4</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E76">
+      <c r="E76" s="1">
         <v>2</v>
       </c>
-      <c r="F76" t="s">
+      <c r="F76" s="1" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D77" t="s">
-        <v>76</v>
-      </c>
-      <c r="E77">
-        <v>2</v>
-      </c>
-      <c r="F77" t="s">
-        <v>79</v>
+        <v>6</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E77" s="1">
+        <v>3</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>68</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D78" t="s">
+        <v>5</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E78">
+      <c r="E78" s="1">
         <v>3</v>
       </c>
-      <c r="F78" t="s">
+      <c r="F78" s="1" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>68</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D79" t="s">
+        <v>4</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E79">
+      <c r="E79" s="1">
         <v>3</v>
       </c>
-      <c r="F79" t="s">
+      <c r="F79" s="1" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D80" t="s">
-        <v>77</v>
-      </c>
-      <c r="E80">
-        <v>3</v>
-      </c>
-      <c r="F80" t="s">
-        <v>80</v>
+        <v>6</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E80" s="1">
+        <v>1</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D81" t="s">
-        <v>75</v>
-      </c>
-      <c r="E81">
-        <v>1</v>
-      </c>
-      <c r="F81" t="s">
+        <v>5</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E81" s="1">
+        <v>1</v>
+      </c>
+      <c r="F81" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D82" t="s">
-        <v>75</v>
-      </c>
-      <c r="E82">
-        <v>1</v>
-      </c>
-      <c r="F82" t="s">
+        <v>4</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E82" s="1">
+        <v>1</v>
+      </c>
+      <c r="F82" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -4854,82 +4855,63 @@
         <v>108</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D83" t="s">
-        <v>75</v>
-      </c>
-      <c r="E83">
-        <v>1</v>
-      </c>
-      <c r="F83" t="s">
+        <v>6</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E83" s="1">
+        <v>1</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>70</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D84" t="s">
-        <v>75</v>
-      </c>
-      <c r="E84">
-        <v>1</v>
-      </c>
-      <c r="F84" t="s">
+        <v>5</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E84" s="1">
+        <v>1</v>
+      </c>
+      <c r="F84" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>70</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D85" t="s">
-        <v>75</v>
-      </c>
-      <c r="E85">
-        <v>1</v>
-      </c>
-      <c r="F85" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D86" t="s">
-        <v>75</v>
-      </c>
-      <c r="E86">
-        <v>1</v>
-      </c>
-      <c r="F86" t="s">
+        <v>4</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E85" s="1">
+        <v>1</v>
+      </c>
+      <c r="F85" s="1" t="s">
         <v>78</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Bases/Navegacao_Menu.xlsx
+++ b/Bases/Navegacao_Menu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djdan\Documents\GitHub\Dash-Upmat\Bases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33BB8D81-8499-441D-9730-CF83CBBEF8A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F126666E-DEE9-43E2-B6DD-BF0E6BE7D71E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23880" yWindow="855" windowWidth="20640" windowHeight="11040" firstSheet="1" activeTab="5" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
+    <workbookView xWindow="23880" yWindow="855" windowWidth="20640" windowHeight="11040" firstSheet="1" activeTab="3" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
   </bookViews>
   <sheets>
     <sheet name="Olitef 2025" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="111">
   <si>
     <t>Ordem</t>
   </si>
@@ -2312,7 +2312,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F446C31-FA66-4630-B110-19ECB8E7DF76}">
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.5703125" bestFit="1" customWidth="1"/>
@@ -2690,37 +2690,37 @@
         <v>20</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>6</v>
@@ -2728,10 +2728,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>6</v>
@@ -2739,112 +2739,104 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>19</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="C39" s="1"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>4</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="C40" s="1"/>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>5</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="C41" s="1"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>15</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="C42" s="1"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>16</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -2852,7 +2844,7 @@
         <v>19</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>6</v>
@@ -2863,48 +2855,126 @@
         <v>20</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
+        <v>20</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>21</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>22</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56">
         <v>23</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B56" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>24</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>25</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>26</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>27</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C60" s="1" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C1" xr:uid="{7F446C31-FA66-4630-B110-19ECB8E7DF76}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Bases/Navegacao_Menu.xlsx
+++ b/Bases/Navegacao_Menu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djdan\Documents\GitHub\Dash-Upmat\Bases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F126666E-DEE9-43E2-B6DD-BF0E6BE7D71E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C19CD7-977A-4D13-A1F0-3AC7C7C33076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23880" yWindow="855" windowWidth="20640" windowHeight="11040" firstSheet="1" activeTab="3" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
+    <workbookView xWindow="23880" yWindow="855" windowWidth="20640" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
   </bookViews>
   <sheets>
     <sheet name="Olitef 2025" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="116">
   <si>
     <t>Ordem</t>
   </si>
@@ -292,9 +292,6 @@
     <t>Canguru Experience 2026</t>
   </si>
   <si>
-    <t>Engajamento Canguru Experience 2026</t>
-  </si>
-  <si>
     <t>Listagem Professores Canguru Experience 2026</t>
   </si>
   <si>
@@ -377,13 +374,31 @@
   </si>
   <si>
     <t>Bebras Experience 2026</t>
+  </si>
+  <si>
+    <t>Engajamento de Professor - Part1</t>
+  </si>
+  <si>
+    <t>Engajamento de Professor - Part2</t>
+  </si>
+  <si>
+    <t>Engajamento Canguru Experience - Part1</t>
+  </si>
+  <si>
+    <t>Engajamento Canguru Experience - Part2</t>
+  </si>
+  <si>
+    <t>Engajamento Canguru Experience - Part3</t>
+  </si>
+  <si>
+    <t>Engajamento Bebras Experience - Part1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -412,6 +427,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -434,11 +455,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2312,7 +2334,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F446C31-FA66-4630-B110-19ECB8E7DF76}">
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C78"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.5703125" bestFit="1" customWidth="1"/>
@@ -2511,7 +2533,7 @@
         <v>6</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>19</v>
@@ -2522,7 +2544,7 @@
         <v>6</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>4</v>
@@ -2533,7 +2555,7 @@
         <v>6</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>5</v>
@@ -2544,7 +2566,7 @@
         <v>6</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>6</v>
@@ -2555,7 +2577,7 @@
         <v>7</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>19</v>
@@ -2566,7 +2588,7 @@
         <v>7</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>4</v>
@@ -2577,7 +2599,7 @@
         <v>7</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>5</v>
@@ -2588,7 +2610,7 @@
         <v>7</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>6</v>
@@ -2599,7 +2621,7 @@
         <v>8</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>19</v>
@@ -2610,7 +2632,7 @@
         <v>8</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>4</v>
@@ -2621,7 +2643,7 @@
         <v>8</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>5</v>
@@ -2632,7 +2654,7 @@
         <v>8</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>6</v>
@@ -2643,7 +2665,7 @@
         <v>9</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>19</v>
@@ -2654,7 +2676,7 @@
         <v>9</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>4</v>
@@ -2665,7 +2687,7 @@
         <v>9</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>5</v>
@@ -2676,7 +2698,7 @@
         <v>9</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>6</v>
@@ -2687,7 +2709,7 @@
         <v>10</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>19</v>
@@ -2698,7 +2720,7 @@
         <v>10</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>4</v>
@@ -2709,7 +2731,7 @@
         <v>10</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>5</v>
@@ -2720,7 +2742,7 @@
         <v>10</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>6</v>
@@ -2731,54 +2753,62 @@
         <v>11</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C39" s="1"/>
+        <v>20</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C40" s="1"/>
+        <v>20</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C41" s="1"/>
+        <v>20</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C42" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>6</v>
@@ -2786,10 +2816,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>6</v>
@@ -2797,177 +2827,375 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C51" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C51" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C52" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C52" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C53" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C53" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>6</v>
+        <v>55</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>6</v>
+        <v>55</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C56" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C56" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>6</v>
+        <v>110</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>6</v>
+        <v>110</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
+        <v>19</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>20</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>20</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>20</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>21</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>21</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>21</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>21</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>22</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>22</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>22</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>22</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>23</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>24</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>25</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>26</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76">
         <v>27</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B76" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>28</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>29</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C78" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2980,7 +3208,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FA0C564-8652-48EB-AFAF-28B449B9D62C}">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.5703125" bestFit="1" customWidth="1"/>
@@ -3047,7 +3275,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>5</v>
@@ -3058,7 +3286,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>6</v>
@@ -3069,7 +3297,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>4</v>
@@ -3080,7 +3308,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>48</v>
@@ -3091,7 +3319,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>5</v>
@@ -3102,7 +3330,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>6</v>
@@ -3113,7 +3341,7 @@
         <v>3</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>4</v>
@@ -3124,7 +3352,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>48</v>
@@ -3135,10 +3363,10 @@
         <v>4</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -3146,10 +3374,10 @@
         <v>4</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -3157,7 +3385,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>4</v>
@@ -3168,9 +3396,9 @@
         <v>4</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C17" t="s">
+        <v>114</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>48</v>
       </c>
     </row>
@@ -3179,10 +3407,10 @@
         <v>5</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -3190,10 +3418,10 @@
         <v>5</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -3201,10 +3429,10 @@
         <v>5</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -3212,9 +3440,9 @@
         <v>5</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>48</v>
       </c>
     </row>
@@ -3223,7 +3451,7 @@
         <v>6</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>6</v>
@@ -3234,10 +3462,10 @@
         <v>6</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -3245,10 +3473,10 @@
         <v>6</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -3256,14 +3484,147 @@
         <v>6</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
         <v>48</v>
       </c>
     </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>7</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>7</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>7</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>7</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>8</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>8</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>8</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>8</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C33" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>9</v>
+      </c>
+      <c r="B34" t="s">
+        <v>115</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>9</v>
+      </c>
+      <c r="B35" t="s">
+        <v>115</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>9</v>
+      </c>
+      <c r="B36" t="s">
+        <v>115</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>9</v>
+      </c>
+      <c r="B37" t="s">
+        <v>115</v>
+      </c>
+      <c r="C37" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3302,7 +3663,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>25</v>
@@ -3322,7 +3683,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>25</v>
@@ -3342,7 +3703,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>25</v>
@@ -3362,7 +3723,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>25</v>
@@ -3382,7 +3743,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>26</v>
@@ -3402,7 +3763,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>26</v>
@@ -3422,7 +3783,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>26</v>
@@ -3442,7 +3803,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>26</v>
@@ -3462,7 +3823,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>39</v>
@@ -3482,7 +3843,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>39</v>
@@ -3502,7 +3863,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>39</v>
@@ -3522,7 +3883,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>39</v>
@@ -3542,7 +3903,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>41</v>
@@ -3562,7 +3923,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>41</v>
@@ -3582,7 +3943,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>41</v>
@@ -3602,7 +3963,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>41</v>
@@ -3622,7 +3983,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>38</v>
@@ -3642,7 +4003,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>38</v>
@@ -3662,7 +4023,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>38</v>
@@ -3682,7 +4043,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>38</v>
@@ -3702,7 +4063,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>37</v>
@@ -3722,7 +4083,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>37</v>
@@ -3742,7 +4103,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>37</v>
@@ -3762,7 +4123,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>37</v>
@@ -3782,7 +4143,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>46</v>
@@ -3802,7 +4163,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>46</v>
@@ -3822,7 +4183,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>46</v>
@@ -3842,7 +4203,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>46</v>
@@ -3862,7 +4223,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>30</v>
@@ -3882,7 +4243,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>30</v>
@@ -3902,7 +4263,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>30</v>
@@ -3922,7 +4283,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>28</v>
@@ -3942,7 +4303,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>28</v>
@@ -3962,7 +4323,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>28</v>
@@ -3982,7 +4343,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>3</v>
@@ -4002,7 +4363,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>3</v>
@@ -4022,7 +4383,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>3</v>
@@ -4042,7 +4403,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>3</v>
@@ -4062,7 +4423,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
@@ -4082,7 +4443,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
@@ -4102,7 +4463,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
@@ -4122,7 +4483,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
@@ -4142,7 +4503,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>40</v>
@@ -4162,7 +4523,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>40</v>
@@ -4182,7 +4543,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>40</v>
@@ -4202,7 +4563,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>62</v>
@@ -4222,7 +4583,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>62</v>
@@ -4242,7 +4603,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>62</v>
@@ -4262,7 +4623,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>61</v>
@@ -4282,7 +4643,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>61</v>
@@ -4302,7 +4663,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>61</v>
@@ -4322,7 +4683,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>60</v>
@@ -4342,7 +4703,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>60</v>
@@ -4362,7 +4723,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>60</v>
@@ -4382,7 +4743,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>35</v>
@@ -4402,7 +4763,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>35</v>
@@ -4422,7 +4783,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>35</v>
@@ -4442,7 +4803,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>34</v>
@@ -4462,7 +4823,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>34</v>
@@ -4482,7 +4843,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>34</v>
@@ -4502,7 +4863,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>63</v>
@@ -4522,7 +4883,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>63</v>
@@ -4542,7 +4903,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>63</v>
@@ -4562,7 +4923,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>64</v>
@@ -4582,7 +4943,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>64</v>
@@ -4602,7 +4963,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>64</v>
@@ -4622,7 +4983,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>65</v>
@@ -4642,7 +5003,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>65</v>
@@ -4662,7 +5023,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>65</v>
@@ -4682,7 +5043,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>66</v>
@@ -4702,7 +5063,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>66</v>
@@ -4722,7 +5083,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>66</v>
@@ -4742,7 +5103,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>67</v>
@@ -4762,7 +5123,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>67</v>
@@ -4782,7 +5143,7 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>67</v>
@@ -4802,7 +5163,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>68</v>
@@ -4822,7 +5183,7 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>68</v>
@@ -4842,7 +5203,7 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>68</v>
@@ -4862,7 +5223,7 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>69</v>
@@ -4882,7 +5243,7 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>69</v>
@@ -4902,7 +5263,7 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>69</v>
@@ -4922,7 +5283,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>70</v>
@@ -4942,7 +5303,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>70</v>
@@ -4962,7 +5323,7 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>70</v>

--- a/Bases/Navegacao_Menu.xlsx
+++ b/Bases/Navegacao_Menu.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djdan\Documents\GitHub\Dash-Upmat\Bases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C19CD7-977A-4D13-A1F0-3AC7C7C33076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DE86319-3608-4864-97FA-3B6E6AF68825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23880" yWindow="855" windowWidth="20640" windowHeight="11040" firstSheet="1" activeTab="4" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" firstSheet="1" activeTab="5" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
   </bookViews>
   <sheets>
     <sheet name="Olitef 2025" sheetId="2" r:id="rId1"/>
@@ -19,8 +19,10 @@
     <sheet name="Olitef 2026" sheetId="5" r:id="rId4"/>
     <sheet name="Experience" sheetId="6" r:id="rId5"/>
     <sheet name="Bebras 2026" sheetId="8" r:id="rId6"/>
+    <sheet name="Medalhas Kangaroo 2026" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Bebras 2026'!$A$1:$F$91</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Olitef 2026'!$A$1:$C$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -44,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="121">
   <si>
     <t>Ordem</t>
   </si>
@@ -392,6 +394,21 @@
   </si>
   <si>
     <t>Engajamento Bebras Experience - Part1</t>
+  </si>
+  <si>
+    <t>Pedidos de Medalhas 2026</t>
+  </si>
+  <si>
+    <t>Potencial de Conversão 2026</t>
+  </si>
+  <si>
+    <t>Itens dos Pedidos 2026</t>
+  </si>
+  <si>
+    <t>1aa</t>
+  </si>
+  <si>
+    <t>1ab</t>
   </si>
 </sst>
 </file>
@@ -3630,7 +3647,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AD31D2E-82F9-4A53-8E31-D57E1126423D}">
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -3638,7 +3655,8 @@
     <col min="3" max="3" width="27.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="6" max="6" width="86.5703125" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4158,7 +4176,7 @@
         <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -4178,7 +4196,7 @@
         <v>1</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -4198,7 +4216,7 @@
         <v>1</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -4218,7 +4236,7 @@
         <v>1</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -4298,7 +4316,7 @@
         <v>2</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -4318,7 +4336,7 @@
         <v>2</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -4338,7 +4356,7 @@
         <v>2</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -4346,19 +4364,19 @@
         <v>93</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E36" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -4366,19 +4384,19 @@
         <v>93</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E37" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -4386,39 +4404,39 @@
         <v>93</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E38" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E39" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -4426,19 +4444,19 @@
         <v>94</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E40" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -4446,30 +4464,30 @@
         <v>94</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E41" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>75</v>
@@ -4483,13 +4501,13 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>75</v>
@@ -4506,10 +4524,10 @@
         <v>95</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>75</v>
@@ -4526,10 +4544,10 @@
         <v>95</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>75</v>
@@ -4543,13 +4561,13 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>75</v>
@@ -4566,19 +4584,19 @@
         <v>96</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E47" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -4586,19 +4604,19 @@
         <v>96</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E48" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -4606,19 +4624,19 @@
         <v>96</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E49" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -4626,19 +4644,19 @@
         <v>97</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E50" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -4646,19 +4664,19 @@
         <v>97</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E51" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -4666,19 +4684,19 @@
         <v>97</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E52" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -4686,19 +4704,19 @@
         <v>98</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E53" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -4706,19 +4724,19 @@
         <v>98</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E54" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -4726,19 +4744,19 @@
         <v>98</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E55" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -4746,19 +4764,19 @@
         <v>99</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E56" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -4766,19 +4784,19 @@
         <v>99</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E57" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -4786,19 +4804,19 @@
         <v>99</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E58" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -4806,19 +4824,19 @@
         <v>100</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E59" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -4826,19 +4844,19 @@
         <v>100</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E60" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -4846,19 +4864,19 @@
         <v>100</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E61" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -4866,7 +4884,7 @@
         <v>101</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>6</v>
@@ -4886,7 +4904,7 @@
         <v>101</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>5</v>
@@ -4906,7 +4924,7 @@
         <v>101</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>4</v>
@@ -4926,7 +4944,7 @@
         <v>102</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>6</v>
@@ -4946,7 +4964,7 @@
         <v>102</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>5</v>
@@ -4966,7 +4984,7 @@
         <v>102</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>4</v>
@@ -4986,7 +5004,7 @@
         <v>103</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>6</v>
@@ -5006,7 +5024,7 @@
         <v>103</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>5</v>
@@ -5026,7 +5044,7 @@
         <v>103</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>4</v>
@@ -5046,19 +5064,19 @@
         <v>104</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E71" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -5066,19 +5084,19 @@
         <v>104</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E72" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -5086,19 +5104,19 @@
         <v>104</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E73" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -5106,19 +5124,19 @@
         <v>105</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E74" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -5126,19 +5144,19 @@
         <v>105</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E75" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -5146,19 +5164,19 @@
         <v>105</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E76" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -5166,19 +5184,19 @@
         <v>108</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E77" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -5186,19 +5204,19 @@
         <v>108</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E78" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -5206,19 +5224,19 @@
         <v>108</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E79" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -5226,19 +5244,19 @@
         <v>106</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E80" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -5246,19 +5264,19 @@
         <v>106</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E81" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -5266,19 +5284,19 @@
         <v>106</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E82" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -5286,19 +5304,19 @@
         <v>107</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E83" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -5306,19 +5324,19 @@
         <v>107</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E84" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -5326,19 +5344,228 @@
         <v>107</v>
       </c>
       <c r="B85" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E85" s="1">
+        <v>3</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E86" s="1">
+        <v>1</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E87" s="1">
+        <v>1</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E88" s="1">
+        <v>1</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C85" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E85" s="1">
-        <v>1</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>78</v>
+      <c r="C89" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E89" s="1">
+        <v>1</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E90" s="1">
+        <v>1</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E91" s="1">
+        <v>1</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F91" xr:uid="{5AD31D2E-82F9-4A53-8E31-D57E1126423D}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5C240E9-AEAB-4CA7-9E20-BE8866BFE0F4}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases/Navegacao_Menu.xlsx
+++ b/Bases/Navegacao_Menu.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\djdan\Documents\GitHub\Dash-Upmat\Bases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DE86319-3608-4864-97FA-3B6E6AF68825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F49BDA2A-2769-440B-8BAF-9D4AC446B566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" firstSheet="1" activeTab="5" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" firstSheet="1" activeTab="4" xr2:uid="{F34CCB2F-E2D2-4F06-83D1-8921BB237BC6}"/>
   </bookViews>
   <sheets>
     <sheet name="Olitef 2025" sheetId="2" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="124">
   <si>
     <t>Ordem</t>
   </si>
@@ -409,6 +409,15 @@
   </si>
   <si>
     <t>1ab</t>
+  </si>
+  <si>
+    <t>Engajamento Bebras Experience - Part2</t>
+  </si>
+  <si>
+    <t>Engajamento Bebras Experience - Part3</t>
+  </si>
+  <si>
+    <t>Listagem Professores Bebras Experience 2026</t>
   </si>
 </sst>
 </file>
@@ -3225,7 +3234,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FA0C564-8652-48EB-AFAF-28B449B9D62C}">
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.5703125" bestFit="1" customWidth="1"/>
@@ -3639,9 +3648,141 @@
         <v>48</v>
       </c>
     </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>10</v>
+      </c>
+      <c r="B38" t="s">
+        <v>121</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>10</v>
+      </c>
+      <c r="B39" t="s">
+        <v>121</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>10</v>
+      </c>
+      <c r="B40" t="s">
+        <v>121</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>10</v>
+      </c>
+      <c r="B41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C41" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>11</v>
+      </c>
+      <c r="B42" t="s">
+        <v>122</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>11</v>
+      </c>
+      <c r="B43" t="s">
+        <v>122</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>11</v>
+      </c>
+      <c r="B44" t="s">
+        <v>122</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>11</v>
+      </c>
+      <c r="B45" t="s">
+        <v>122</v>
+      </c>
+      <c r="C45" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>12</v>
+      </c>
+      <c r="B46" t="s">
+        <v>123</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>12</v>
+      </c>
+      <c r="B47" t="s">
+        <v>123</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>12</v>
+      </c>
+      <c r="B48" t="s">
+        <v>123</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>12</v>
+      </c>
+      <c r="B49" t="s">
+        <v>123</v>
+      </c>
+      <c r="C49" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
 </worksheet>
 </file>
 
